--- a/research/traditional_assets/database/data/argentina/argentina_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_metals_mining.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.2461145440997959</v>
+        <v>0.2452823931954466</v>
       </c>
       <c r="C2">
-        <v>3084.484964625905</v>
+        <v>3065.409052966495</v>
       </c>
       <c r="D2">
-        <v>2829.184964625905</v>
+        <v>2840.987052966495</v>
       </c>
       <c r="E2">
-        <v>-665.1</v>
+        <v>-634.222</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>30.878</v>
       </c>
       <c r="G2">
         <v>255.3</v>
@@ -1451,28 +1451,28 @@
         <v>214.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.5531634</v>
       </c>
       <c r="N2">
-        <v>214.4</v>
+        <v>212.8468366</v>
       </c>
       <c r="O2">
-        <v>75.03999999999999</v>
+        <v>74.49639281</v>
       </c>
       <c r="P2">
-        <v>139.36</v>
+        <v>138.35044379</v>
       </c>
       <c r="Q2">
-        <v>207.66</v>
+        <v>206.65044379</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.2461145440997959</v>
+        <v>0.2474297406014613</v>
       </c>
       <c r="T2">
-        <v>0.9842199092652959</v>
+        <v>0.9906819591746135</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>138.0408526237485</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.2452823931954466</v>
+        <v>0.2444502422910974</v>
       </c>
       <c r="C3">
-        <v>3065.409052966495</v>
+        <v>3046.432019801995</v>
       </c>
       <c r="D3">
-        <v>2840.987052966495</v>
+        <v>2852.888019801995</v>
       </c>
       <c r="E3">
-        <v>-634.222</v>
+        <v>-603.3440000000001</v>
       </c>
       <c r="F3">
-        <v>30.878</v>
+        <v>61.75599999999999</v>
       </c>
       <c r="G3">
         <v>255.3</v>
@@ -1533,28 +1533,28 @@
         <v>214.4</v>
       </c>
       <c r="M3">
-        <v>1.5531634</v>
+        <v>3.106326799999999</v>
       </c>
       <c r="N3">
-        <v>212.8468366</v>
+        <v>211.2936732</v>
       </c>
       <c r="O3">
-        <v>74.49639281</v>
+        <v>73.95278562</v>
       </c>
       <c r="P3">
-        <v>138.35044379</v>
+        <v>137.34088758</v>
       </c>
       <c r="Q3">
-        <v>206.65044379</v>
+        <v>205.64088758</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.2474297406014613</v>
+        <v>0.2487717778480585</v>
       </c>
       <c r="T3">
-        <v>0.9906819591746135</v>
+        <v>0.9972758876535091</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>138.0408526237485</v>
+        <v>69.02042631187422</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.2444502422910974</v>
+        <v>0.243618091386748</v>
       </c>
       <c r="C4">
-        <v>3046.432019801995</v>
+        <v>3027.555112973217</v>
       </c>
       <c r="D4">
-        <v>2852.888019801995</v>
+        <v>2864.889112973217</v>
       </c>
       <c r="E4">
-        <v>-603.3440000000001</v>
+        <v>-572.466</v>
       </c>
       <c r="F4">
-        <v>61.75599999999999</v>
+        <v>92.63399999999999</v>
       </c>
       <c r="G4">
         <v>255.3</v>
@@ -1615,28 +1615,28 @@
         <v>214.4</v>
       </c>
       <c r="M4">
-        <v>3.106326799999999</v>
+        <v>4.659490199999999</v>
       </c>
       <c r="N4">
-        <v>211.2936732</v>
+        <v>209.7405098</v>
       </c>
       <c r="O4">
-        <v>73.95278562</v>
+        <v>73.40917843</v>
       </c>
       <c r="P4">
-        <v>137.34088758</v>
+        <v>136.33133137</v>
       </c>
       <c r="Q4">
-        <v>205.64088758</v>
+        <v>204.63133137</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2487717778480585</v>
+        <v>0.2501414859657196</v>
       </c>
       <c r="T4">
-        <v>0.9972758876535091</v>
+        <v>1.004005773420629</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>69.02042631187422</v>
+        <v>46.01361754124949</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.243618091386748</v>
+        <v>0.2427859404823988</v>
       </c>
       <c r="C5">
-        <v>3027.555112973217</v>
+        <v>3008.779601406568</v>
       </c>
       <c r="D5">
-        <v>2864.889112973217</v>
+        <v>2876.991601406568</v>
       </c>
       <c r="E5">
-        <v>-572.466</v>
+        <v>-541.5880000000001</v>
       </c>
       <c r="F5">
-        <v>92.63399999999999</v>
+        <v>123.512</v>
       </c>
       <c r="G5">
         <v>255.3</v>
@@ -1697,28 +1697,28 @@
         <v>214.4</v>
       </c>
       <c r="M5">
-        <v>4.659490199999999</v>
+        <v>6.212653599999999</v>
       </c>
       <c r="N5">
-        <v>209.7405098</v>
+        <v>208.1873464</v>
       </c>
       <c r="O5">
-        <v>73.40917843</v>
+        <v>72.86557123999999</v>
       </c>
       <c r="P5">
-        <v>136.33133137</v>
+        <v>135.32177516</v>
       </c>
       <c r="Q5">
-        <v>204.63133137</v>
+        <v>203.62177516</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2501414859657196</v>
+        <v>0.2515397296691654</v>
       </c>
       <c r="T5">
-        <v>1.004005773420629</v>
+        <v>1.010875865141231</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>46.01361754124949</v>
+        <v>34.51021315593711</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2427859404823988</v>
+        <v>0.2419537895780494</v>
       </c>
       <c r="C6">
-        <v>3008.779601406568</v>
+        <v>2990.106775561327</v>
       </c>
       <c r="D6">
-        <v>2876.991601406568</v>
+        <v>2889.196775561326</v>
       </c>
       <c r="E6">
-        <v>-541.5880000000001</v>
+        <v>-510.71</v>
       </c>
       <c r="F6">
-        <v>123.512</v>
+        <v>154.39</v>
       </c>
       <c r="G6">
         <v>255.3</v>
@@ -1779,28 +1779,28 @@
         <v>214.4</v>
       </c>
       <c r="M6">
-        <v>6.212653599999999</v>
+        <v>7.765816999999999</v>
       </c>
       <c r="N6">
-        <v>208.1873464</v>
+        <v>206.634183</v>
       </c>
       <c r="O6">
-        <v>72.86557123999999</v>
+        <v>72.32196404999999</v>
       </c>
       <c r="P6">
-        <v>135.32177516</v>
+        <v>134.31221895</v>
       </c>
       <c r="Q6">
-        <v>203.62177516</v>
+        <v>202.61221895</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2515397296691654</v>
+        <v>0.2529674100821573</v>
       </c>
       <c r="T6">
-        <v>1.010875865141231</v>
+        <v>1.01789059037174</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>34.51021315593711</v>
+        <v>27.60817052474968</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2419537895780494</v>
+        <v>0.2411216386737002</v>
       </c>
       <c r="C7">
-        <v>2990.106775561327</v>
+        <v>2971.537947888325</v>
       </c>
       <c r="D7">
-        <v>2889.196775561326</v>
+        <v>2901.505947888325</v>
       </c>
       <c r="E7">
-        <v>-510.71</v>
+        <v>-479.832</v>
       </c>
       <c r="F7">
-        <v>154.39</v>
+        <v>185.268</v>
       </c>
       <c r="G7">
         <v>255.3</v>
@@ -1861,28 +1861,28 @@
         <v>214.4</v>
       </c>
       <c r="M7">
-        <v>7.765816999999999</v>
+        <v>9.318980399999999</v>
       </c>
       <c r="N7">
-        <v>206.634183</v>
+        <v>205.0810196</v>
       </c>
       <c r="O7">
-        <v>72.32196404999999</v>
+        <v>71.77835686</v>
       </c>
       <c r="P7">
-        <v>134.31221895</v>
+        <v>133.30266274</v>
       </c>
       <c r="Q7">
-        <v>202.61221895</v>
+        <v>201.60266274</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.2529674100821573</v>
+        <v>0.2544254666741491</v>
       </c>
       <c r="T7">
-        <v>1.01789059037174</v>
+        <v>1.025054565075239</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>27.60817052474968</v>
+        <v>23.00680877062474</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.2411216386737002</v>
+        <v>0.2402894877693509</v>
       </c>
       <c r="C8">
-        <v>2971.537947888325</v>
+        <v>2953.07445330043</v>
       </c>
       <c r="D8">
-        <v>2901.505947888325</v>
+        <v>2913.920453300429</v>
       </c>
       <c r="E8">
-        <v>-479.8320000000001</v>
+        <v>-448.9540000000001</v>
       </c>
       <c r="F8">
-        <v>185.268</v>
+        <v>216.146</v>
       </c>
       <c r="G8">
         <v>255.3</v>
@@ -1943,28 +1943,28 @@
         <v>214.4</v>
       </c>
       <c r="M8">
-        <v>9.318980399999997</v>
+        <v>10.8721438</v>
       </c>
       <c r="N8">
-        <v>205.0810196</v>
+        <v>203.5278562</v>
       </c>
       <c r="O8">
-        <v>71.77835686</v>
+        <v>71.23474967</v>
       </c>
       <c r="P8">
-        <v>133.30266274</v>
+        <v>132.29310653</v>
       </c>
       <c r="Q8">
-        <v>201.60266274</v>
+        <v>200.59310653</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2544254666741491</v>
+        <v>0.2559148793218827</v>
       </c>
       <c r="T8">
-        <v>1.025054565075239</v>
+        <v>1.032372603750856</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.00680877062474</v>
+        <v>19.72012180339263</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.2402894877693509</v>
+        <v>0.2394573368650016</v>
       </c>
       <c r="C9">
-        <v>2953.07445330043</v>
+        <v>2934.717649655135</v>
       </c>
       <c r="D9">
-        <v>2913.92045330043</v>
+        <v>2926.441649655134</v>
       </c>
       <c r="E9">
-        <v>-448.954</v>
+        <v>-418.076</v>
       </c>
       <c r="F9">
-        <v>216.146</v>
+        <v>247.024</v>
       </c>
       <c r="G9">
         <v>255.3</v>
@@ -2025,28 +2025,28 @@
         <v>214.4</v>
       </c>
       <c r="M9">
-        <v>10.8721438</v>
+        <v>12.4253072</v>
       </c>
       <c r="N9">
-        <v>203.5278562</v>
+        <v>201.9746928</v>
       </c>
       <c r="O9">
-        <v>71.23474967</v>
+        <v>70.69114248</v>
       </c>
       <c r="P9">
-        <v>132.29310653</v>
+        <v>131.28355032</v>
       </c>
       <c r="Q9">
-        <v>200.59310653</v>
+        <v>199.58355032</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2559148793218827</v>
+        <v>0.2574366705054365</v>
       </c>
       <c r="T9">
-        <v>1.032372603750856</v>
+        <v>1.039849730223769</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.72012180339263</v>
+        <v>17.25510657796855</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2394573368650016</v>
+        <v>0.2386251859606523</v>
       </c>
       <c r="C10">
-        <v>2934.717649655135</v>
+        <v>2916.468918249658</v>
       </c>
       <c r="D10">
-        <v>2926.441649655134</v>
+        <v>2939.070918249658</v>
       </c>
       <c r="E10">
-        <v>-418.076</v>
+        <v>-387.198</v>
       </c>
       <c r="F10">
-        <v>247.024</v>
+        <v>277.902</v>
       </c>
       <c r="G10">
         <v>255.3</v>
@@ -2107,28 +2107,28 @@
         <v>214.4</v>
       </c>
       <c r="M10">
-        <v>12.4253072</v>
+        <v>13.9784706</v>
       </c>
       <c r="N10">
-        <v>201.9746928</v>
+        <v>200.4215294</v>
       </c>
       <c r="O10">
-        <v>70.69114248</v>
+        <v>70.14753528999999</v>
       </c>
       <c r="P10">
-        <v>131.28355032</v>
+        <v>130.27399411</v>
       </c>
       <c r="Q10">
-        <v>199.58355032</v>
+        <v>198.57399411</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2574366705054365</v>
+        <v>0.2589919076490685</v>
       </c>
       <c r="T10">
-        <v>1.039849730223769</v>
+        <v>1.047491189146636</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.25510657796855</v>
+        <v>15.33787251374983</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.2386251859606523</v>
+        <v>0.2377930350563031</v>
       </c>
       <c r="C11">
-        <v>2916.468918249658</v>
+        <v>2898.329664328914</v>
       </c>
       <c r="D11">
-        <v>2939.070918249658</v>
+        <v>2951.809664328914</v>
       </c>
       <c r="E11">
-        <v>-387.198</v>
+        <v>-356.3200000000001</v>
       </c>
       <c r="F11">
-        <v>277.902</v>
+        <v>308.78</v>
       </c>
       <c r="G11">
         <v>255.3</v>
@@ -2189,28 +2189,28 @@
         <v>214.4</v>
       </c>
       <c r="M11">
-        <v>13.9784706</v>
+        <v>15.531634</v>
       </c>
       <c r="N11">
-        <v>200.4215294</v>
+        <v>198.868366</v>
       </c>
       <c r="O11">
-        <v>70.14753528999999</v>
+        <v>69.6039281</v>
       </c>
       <c r="P11">
-        <v>130.27399411</v>
+        <v>129.2644379</v>
       </c>
       <c r="Q11">
-        <v>198.57399411</v>
+        <v>197.5644379</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2589919076490685</v>
+        <v>0.2605817056181145</v>
       </c>
       <c r="T11">
-        <v>1.047491189146636</v>
+        <v>1.055302458267789</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.33787251374983</v>
+        <v>13.80408526237484</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.2377930350563031</v>
+        <v>0.2370681341519538</v>
       </c>
       <c r="C12">
-        <v>2898.329664328914</v>
+        <v>2878.638940790967</v>
       </c>
       <c r="D12">
-        <v>2951.809664328914</v>
+        <v>2962.996940790967</v>
       </c>
       <c r="E12">
-        <v>-356.3200000000001</v>
+        <v>-325.4420000000001</v>
       </c>
       <c r="F12">
-        <v>308.78</v>
+        <v>339.658</v>
       </c>
       <c r="G12">
         <v>255.3</v>
@@ -2271,45 +2271,45 @@
         <v>214.4</v>
       </c>
       <c r="M12">
-        <v>15.531634</v>
+        <v>17.5942844</v>
       </c>
       <c r="N12">
-        <v>198.868366</v>
+        <v>196.8057156</v>
       </c>
       <c r="O12">
-        <v>69.6039281</v>
+        <v>68.88200046</v>
       </c>
       <c r="P12">
-        <v>129.2644379</v>
+        <v>127.92371514</v>
       </c>
       <c r="Q12">
-        <v>197.5644379</v>
+        <v>196.22371514</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2605817056181145</v>
+        <v>0.2622072293842178</v>
       </c>
       <c r="T12">
-        <v>1.055302458267789</v>
+        <v>1.063289261526497</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.35</v>
       </c>
       <c r="W12">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.80408526237484</v>
+        <v>12.18577551241584</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.2370681341519538</v>
+        <v>0.2362457332476045</v>
       </c>
       <c r="C13">
-        <v>2878.638940790967</v>
+        <v>2860.556036391888</v>
       </c>
       <c r="D13">
-        <v>2962.996940790967</v>
+        <v>2975.792036391888</v>
       </c>
       <c r="E13">
-        <v>-325.4420000000001</v>
+        <v>-294.5640000000001</v>
       </c>
       <c r="F13">
-        <v>339.658</v>
+        <v>370.5359999999999</v>
       </c>
       <c r="G13">
         <v>255.3</v>
@@ -2353,28 +2353,28 @@
         <v>214.4</v>
       </c>
       <c r="M13">
-        <v>17.5942844</v>
+        <v>19.1937648</v>
       </c>
       <c r="N13">
-        <v>196.8057156</v>
+        <v>195.2062352</v>
       </c>
       <c r="O13">
-        <v>68.88200046</v>
+        <v>68.32218232</v>
       </c>
       <c r="P13">
-        <v>127.92371514</v>
+        <v>126.88405288</v>
       </c>
       <c r="Q13">
-        <v>196.22371514</v>
+        <v>195.18405288</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2622072293842178</v>
+        <v>0.2638696968722778</v>
       </c>
       <c r="T13">
-        <v>1.063289261526497</v>
+        <v>1.071457583041084</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.18577551241584</v>
+        <v>11.17029421971452</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.2362457332476045</v>
+        <v>0.2354233323432552</v>
       </c>
       <c r="C14">
-        <v>2860.556036391888</v>
+        <v>2842.584117260957</v>
       </c>
       <c r="D14">
-        <v>2975.792036391888</v>
+        <v>2988.698117260957</v>
       </c>
       <c r="E14">
-        <v>-294.5640000000001</v>
+        <v>-263.686</v>
       </c>
       <c r="F14">
-        <v>370.5359999999999</v>
+        <v>401.414</v>
       </c>
       <c r="G14">
         <v>255.3</v>
@@ -2435,28 +2435,28 @@
         <v>214.4</v>
       </c>
       <c r="M14">
-        <v>19.1937648</v>
+        <v>20.7932452</v>
       </c>
       <c r="N14">
-        <v>195.2062352</v>
+        <v>193.6067548</v>
       </c>
       <c r="O14">
-        <v>68.32218232</v>
+        <v>67.76236417999999</v>
       </c>
       <c r="P14">
-        <v>126.88405288</v>
+        <v>125.84439062</v>
       </c>
       <c r="Q14">
-        <v>195.18405288</v>
+        <v>194.14439062</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2638696968722778</v>
+        <v>0.2655703820037416</v>
       </c>
       <c r="T14">
-        <v>1.071457583041084</v>
+        <v>1.079813682061753</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.17029421971452</v>
+        <v>10.31104081819802</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.2354233323432552</v>
+        <v>0.234755631438906</v>
       </c>
       <c r="C15">
-        <v>2842.584117260957</v>
+        <v>2822.267096155979</v>
       </c>
       <c r="D15">
-        <v>2988.698117260957</v>
+        <v>2999.259096155979</v>
       </c>
       <c r="E15">
-        <v>-263.686</v>
+        <v>-232.808</v>
       </c>
       <c r="F15">
-        <v>401.414</v>
+        <v>432.292</v>
       </c>
       <c r="G15">
         <v>255.3</v>
@@ -2517,45 +2517,45 @@
         <v>214.4</v>
       </c>
       <c r="M15">
-        <v>20.7932452</v>
+        <v>23.127622</v>
       </c>
       <c r="N15">
-        <v>193.6067548</v>
+        <v>191.272378</v>
       </c>
       <c r="O15">
-        <v>67.76236417999999</v>
+        <v>66.9453323</v>
       </c>
       <c r="P15">
-        <v>125.84439062</v>
+        <v>124.3270457</v>
       </c>
       <c r="Q15">
-        <v>194.14439062</v>
+        <v>192.6270457</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2655703820037416</v>
+        <v>0.2673106179522162</v>
       </c>
       <c r="T15">
-        <v>1.079813682061753</v>
+        <v>1.088364108966624</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.35</v>
       </c>
       <c r="W15">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.31104081819802</v>
+        <v>9.270300249632236</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.234755631438906</v>
+        <v>0.2339442805345566</v>
       </c>
       <c r="C16">
-        <v>2822.267096155979</v>
+        <v>2804.323061372089</v>
       </c>
       <c r="D16">
-        <v>2999.259096155979</v>
+        <v>3012.193061372089</v>
       </c>
       <c r="E16">
-        <v>-232.808</v>
+        <v>-201.93</v>
       </c>
       <c r="F16">
-        <v>432.292</v>
+        <v>463.17</v>
       </c>
       <c r="G16">
         <v>255.3</v>
@@ -2599,28 +2599,28 @@
         <v>214.4</v>
       </c>
       <c r="M16">
-        <v>23.127622</v>
+        <v>24.779595</v>
       </c>
       <c r="N16">
-        <v>191.272378</v>
+        <v>189.620405</v>
       </c>
       <c r="O16">
-        <v>66.9453323</v>
+        <v>66.36714175</v>
       </c>
       <c r="P16">
-        <v>124.3270457</v>
+        <v>123.25326325</v>
       </c>
       <c r="Q16">
-        <v>192.6270457</v>
+        <v>191.55326325</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2673106179522162</v>
+        <v>0.2690918006288902</v>
       </c>
       <c r="T16">
-        <v>1.088364108966624</v>
+        <v>1.097115722386903</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.270300249632236</v>
+        <v>8.652280232990087</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.2339442805345566</v>
+        <v>0.2331329296302074</v>
       </c>
       <c r="C17">
-        <v>2804.323061372089</v>
+        <v>2786.491062250009</v>
       </c>
       <c r="D17">
-        <v>3012.193061372089</v>
+        <v>3025.239062250008</v>
       </c>
       <c r="E17">
-        <v>-201.9300000000001</v>
+        <v>-171.0520000000001</v>
       </c>
       <c r="F17">
-        <v>463.17</v>
+        <v>494.0479999999999</v>
       </c>
       <c r="G17">
         <v>255.3</v>
@@ -2681,28 +2681,28 @@
         <v>214.4</v>
       </c>
       <c r="M17">
-        <v>24.779595</v>
+        <v>26.431568</v>
       </c>
       <c r="N17">
-        <v>189.620405</v>
+        <v>187.968432</v>
       </c>
       <c r="O17">
-        <v>66.36714175</v>
+        <v>65.7889512</v>
       </c>
       <c r="P17">
-        <v>123.25326325</v>
+        <v>122.1794808</v>
       </c>
       <c r="Q17">
-        <v>191.55326325</v>
+        <v>190.4794808</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2690918006288902</v>
+        <v>0.2709153924169135</v>
       </c>
       <c r="T17">
-        <v>1.097115722386903</v>
+        <v>1.106075707555285</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.652280232990089</v>
+        <v>8.111512718428209</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.2331329296302074</v>
+        <v>0.232321578725858</v>
       </c>
       <c r="C18">
-        <v>2786.491062250009</v>
+        <v>2768.772560822756</v>
       </c>
       <c r="D18">
-        <v>3025.239062250008</v>
+        <v>3038.398560822756</v>
       </c>
       <c r="E18">
-        <v>-171.0520000000001</v>
+        <v>-140.174</v>
       </c>
       <c r="F18">
-        <v>494.0479999999999</v>
+        <v>524.926</v>
       </c>
       <c r="G18">
         <v>255.3</v>
@@ -2763,28 +2763,28 @@
         <v>214.4</v>
       </c>
       <c r="M18">
-        <v>26.431568</v>
+        <v>28.083541</v>
       </c>
       <c r="N18">
-        <v>187.968432</v>
+        <v>186.316459</v>
       </c>
       <c r="O18">
-        <v>65.7889512</v>
+        <v>65.21076065</v>
       </c>
       <c r="P18">
-        <v>122.1794808</v>
+        <v>121.10569835</v>
       </c>
       <c r="Q18">
-        <v>190.4794808</v>
+        <v>189.40569835</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2709153924169135</v>
+        <v>0.2727829261757326</v>
       </c>
       <c r="T18">
-        <v>1.106075707555285</v>
+        <v>1.115251595980736</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.111512718428209</v>
+        <v>7.634364911461842</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.232321578725858</v>
+        <v>0.2316038278215088</v>
       </c>
       <c r="C19">
-        <v>2768.772560822756</v>
+        <v>2749.631742668649</v>
       </c>
       <c r="D19">
-        <v>3038.398560822756</v>
+        <v>3050.135742668649</v>
       </c>
       <c r="E19">
-        <v>-140.174</v>
+        <v>-109.296</v>
       </c>
       <c r="F19">
-        <v>524.926</v>
+        <v>555.804</v>
       </c>
       <c r="G19">
         <v>255.3</v>
@@ -2845,45 +2845,45 @@
         <v>214.4</v>
       </c>
       <c r="M19">
-        <v>28.083541</v>
+        <v>30.1801572</v>
       </c>
       <c r="N19">
-        <v>186.316459</v>
+        <v>184.2198428</v>
       </c>
       <c r="O19">
-        <v>65.21076065</v>
+        <v>64.47694498</v>
       </c>
       <c r="P19">
-        <v>121.10569835</v>
+        <v>119.74289782</v>
       </c>
       <c r="Q19">
-        <v>189.40569835</v>
+        <v>188.04289782</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2727829261757326</v>
+        <v>0.2746960095384253</v>
       </c>
       <c r="T19">
-        <v>1.115251595980736</v>
+        <v>1.124651286562905</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.35</v>
       </c>
       <c r="W19">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>7.634364911461842</v>
+        <v>7.104005409222984</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.2316038278215088</v>
+        <v>0.2307976769171595</v>
       </c>
       <c r="C20">
-        <v>2749.631742668648</v>
+        <v>2732.045097070042</v>
       </c>
       <c r="D20">
-        <v>3050.135742668648</v>
+        <v>3063.427097070041</v>
       </c>
       <c r="E20">
-        <v>-109.296</v>
+        <v>-78.41800000000012</v>
       </c>
       <c r="F20">
-        <v>555.804</v>
+        <v>586.6819999999999</v>
       </c>
       <c r="G20">
         <v>255.3</v>
@@ -2927,28 +2927,28 @@
         <v>214.4</v>
       </c>
       <c r="M20">
-        <v>30.1801572</v>
+        <v>31.8568326</v>
       </c>
       <c r="N20">
-        <v>184.2198428</v>
+        <v>182.5431674</v>
       </c>
       <c r="O20">
-        <v>64.47694498</v>
+        <v>63.89010859</v>
       </c>
       <c r="P20">
-        <v>119.74289782</v>
+        <v>118.65305881</v>
       </c>
       <c r="Q20">
-        <v>188.04289782</v>
+        <v>186.95305881</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2746960095384253</v>
+        <v>0.2766563295273574</v>
       </c>
       <c r="T20">
-        <v>1.124651286562905</v>
+        <v>1.13428306827056</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.104005409222984</v>
+        <v>6.730110387684934</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.2307976769171595</v>
+        <v>0.2299915260128103</v>
       </c>
       <c r="C21">
-        <v>2732.045097070042</v>
+        <v>2714.574795991757</v>
       </c>
       <c r="D21">
-        <v>3063.427097070041</v>
+        <v>3076.834795991756</v>
       </c>
       <c r="E21">
-        <v>-78.41800000000012</v>
+        <v>-47.54000000000008</v>
       </c>
       <c r="F21">
-        <v>586.6819999999999</v>
+        <v>617.5599999999999</v>
       </c>
       <c r="G21">
         <v>255.3</v>
@@ -3009,28 +3009,28 @@
         <v>214.4</v>
       </c>
       <c r="M21">
-        <v>31.8568326</v>
+        <v>33.533508</v>
       </c>
       <c r="N21">
-        <v>182.5431674</v>
+        <v>180.866492</v>
       </c>
       <c r="O21">
-        <v>63.89010859</v>
+        <v>63.30327219999999</v>
       </c>
       <c r="P21">
-        <v>118.65305881</v>
+        <v>117.5632198</v>
       </c>
       <c r="Q21">
-        <v>186.95305881</v>
+        <v>185.8632198</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2766563295273574</v>
+        <v>0.2786656575160128</v>
       </c>
       <c r="T21">
-        <v>1.13428306827056</v>
+        <v>1.144155644520907</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.730110387684934</v>
+        <v>6.393604868300686</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.2299915260128103</v>
+        <v>0.2293218751084609</v>
       </c>
       <c r="C22">
-        <v>2714.574795991757</v>
+        <v>2694.923823845803</v>
       </c>
       <c r="D22">
-        <v>3076.834795991756</v>
+        <v>3088.061823845803</v>
       </c>
       <c r="E22">
-        <v>-47.54000000000008</v>
+        <v>-16.66200000000003</v>
       </c>
       <c r="F22">
-        <v>617.5599999999999</v>
+        <v>648.438</v>
       </c>
       <c r="G22">
         <v>255.3</v>
@@ -3091,45 +3091,45 @@
         <v>214.4</v>
       </c>
       <c r="M22">
-        <v>33.533508</v>
+        <v>35.8586214</v>
       </c>
       <c r="N22">
-        <v>180.866492</v>
+        <v>178.5413786</v>
       </c>
       <c r="O22">
-        <v>63.30327219999999</v>
+        <v>62.48948250999999</v>
       </c>
       <c r="P22">
-        <v>117.5632198</v>
+        <v>116.05189609</v>
       </c>
       <c r="Q22">
-        <v>185.8632198</v>
+        <v>184.35189609</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2786656575160128</v>
+        <v>0.280725854567672</v>
       </c>
       <c r="T22">
-        <v>1.144155644520907</v>
+        <v>1.154278159410502</v>
       </c>
       <c r="U22">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.35</v>
       </c>
       <c r="W22">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.393604868300686</v>
+        <v>5.979036327369796</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2293218751084609</v>
+        <v>0.2285222242041117</v>
       </c>
       <c r="C23">
-        <v>2694.923823845803</v>
+        <v>2677.560170230763</v>
       </c>
       <c r="D23">
-        <v>3088.061823845803</v>
+        <v>3101.576170230762</v>
       </c>
       <c r="E23">
-        <v>-16.66200000000015</v>
+        <v>14.21599999999989</v>
       </c>
       <c r="F23">
-        <v>648.4379999999999</v>
+        <v>679.3159999999999</v>
       </c>
       <c r="G23">
         <v>255.3</v>
@@ -3173,28 +3173,28 @@
         <v>214.4</v>
       </c>
       <c r="M23">
-        <v>35.8586214</v>
+        <v>37.5661748</v>
       </c>
       <c r="N23">
-        <v>178.5413786</v>
+        <v>176.8338252</v>
       </c>
       <c r="O23">
-        <v>62.48948250999999</v>
+        <v>61.89183882</v>
       </c>
       <c r="P23">
-        <v>116.05189609</v>
+        <v>114.94198638</v>
       </c>
       <c r="Q23">
-        <v>184.35189609</v>
+        <v>183.24198638</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.280725854567672</v>
+        <v>0.2828388771847585</v>
       </c>
       <c r="T23">
-        <v>1.154278159410502</v>
+        <v>1.164660225963934</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.979036327369797</v>
+        <v>5.707261948852988</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.2285222242041117</v>
+        <v>0.2277225732997624</v>
       </c>
       <c r="C24">
-        <v>2677.560170230763</v>
+        <v>2660.315322755197</v>
       </c>
       <c r="D24">
-        <v>3101.576170230762</v>
+        <v>3115.209322755197</v>
       </c>
       <c r="E24">
-        <v>14.21599999999989</v>
+        <v>45.09399999999994</v>
       </c>
       <c r="F24">
-        <v>679.3159999999999</v>
+        <v>710.194</v>
       </c>
       <c r="G24">
         <v>255.3</v>
@@ -3255,28 +3255,28 @@
         <v>214.4</v>
       </c>
       <c r="M24">
-        <v>37.5661748</v>
+        <v>39.2737282</v>
       </c>
       <c r="N24">
-        <v>176.8338252</v>
+        <v>175.1262718</v>
       </c>
       <c r="O24">
-        <v>61.89183882</v>
+        <v>61.29419513</v>
       </c>
       <c r="P24">
-        <v>114.94198638</v>
+        <v>113.83207667</v>
       </c>
       <c r="Q24">
-        <v>183.24198638</v>
+        <v>182.13207667</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2828388771847585</v>
+        <v>0.2850067835061849</v>
       </c>
       <c r="T24">
-        <v>1.164660225963934</v>
+        <v>1.175311956583688</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.707261948852988</v>
+        <v>5.459120124989814</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2277225732997624</v>
+        <v>0.2269229223954131</v>
       </c>
       <c r="C25">
-        <v>2660.315322755197</v>
+        <v>2643.190854993045</v>
       </c>
       <c r="D25">
-        <v>3115.209322755197</v>
+        <v>3128.962854993045</v>
       </c>
       <c r="E25">
-        <v>45.09399999999994</v>
+        <v>75.97199999999998</v>
       </c>
       <c r="F25">
-        <v>710.194</v>
+        <v>741.072</v>
       </c>
       <c r="G25">
         <v>255.3</v>
@@ -3337,28 +3337,28 @@
         <v>214.4</v>
       </c>
       <c r="M25">
-        <v>39.2737282</v>
+        <v>40.9812816</v>
       </c>
       <c r="N25">
-        <v>175.1262718</v>
+        <v>173.4187184</v>
       </c>
       <c r="O25">
-        <v>61.29419513</v>
+        <v>60.69655143999999</v>
       </c>
       <c r="P25">
-        <v>113.83207667</v>
+        <v>112.72216696</v>
       </c>
       <c r="Q25">
-        <v>182.13207667</v>
+        <v>181.02216696</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2850067835061849</v>
+        <v>0.2872317399939646</v>
       </c>
       <c r="T25">
-        <v>1.175311956583688</v>
+        <v>1.186243995903962</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.459120124989814</v>
+        <v>5.231656786448571</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2269229223954131</v>
+        <v>0.2261232714910638</v>
       </c>
       <c r="C26">
-        <v>2643.190854993045</v>
+        <v>2626.188368430558</v>
       </c>
       <c r="D26">
-        <v>3128.962854993045</v>
+        <v>3142.838368430557</v>
       </c>
       <c r="E26">
-        <v>75.97199999999987</v>
+        <v>106.8499999999999</v>
       </c>
       <c r="F26">
-        <v>741.0719999999999</v>
+        <v>771.9499999999999</v>
       </c>
       <c r="G26">
         <v>255.3</v>
@@ -3419,28 +3419,28 @@
         <v>214.4</v>
       </c>
       <c r="M26">
-        <v>40.9812816</v>
+        <v>42.688835</v>
       </c>
       <c r="N26">
-        <v>173.4187184</v>
+        <v>171.711165</v>
       </c>
       <c r="O26">
-        <v>60.69655144</v>
+        <v>60.09890775</v>
       </c>
       <c r="P26">
-        <v>112.72216696</v>
+        <v>111.61225725</v>
       </c>
       <c r="Q26">
-        <v>181.02216696</v>
+        <v>179.91225725</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2872317399939646</v>
+        <v>0.2895160286547517</v>
       </c>
       <c r="T26">
-        <v>1.186243995903962</v>
+        <v>1.197467556272777</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.231656786448573</v>
+        <v>5.022390514990629</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.2261232714910638</v>
+        <v>0.2253236205867145</v>
       </c>
       <c r="C27">
-        <v>2626.188368430558</v>
+        <v>2609.309493087947</v>
       </c>
       <c r="D27">
-        <v>3142.838368430557</v>
+        <v>3156.837493087946</v>
       </c>
       <c r="E27">
-        <v>106.8499999999999</v>
+        <v>137.728</v>
       </c>
       <c r="F27">
-        <v>771.9499999999999</v>
+        <v>802.828</v>
       </c>
       <c r="G27">
         <v>255.3</v>
@@ -3501,28 +3501,28 @@
         <v>214.4</v>
       </c>
       <c r="M27">
-        <v>42.688835</v>
+        <v>44.3963884</v>
       </c>
       <c r="N27">
-        <v>171.711165</v>
+        <v>170.0036116</v>
       </c>
       <c r="O27">
-        <v>60.09890775</v>
+        <v>59.50126406</v>
       </c>
       <c r="P27">
-        <v>111.61225725</v>
+        <v>110.50234754</v>
       </c>
       <c r="Q27">
-        <v>179.91225725</v>
+        <v>178.80234754</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2895160286547517</v>
+        <v>0.2918620548469115</v>
       </c>
       <c r="T27">
-        <v>1.197467556272777</v>
+        <v>1.208994456111019</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.022390514990629</v>
+        <v>4.829221649029451</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2253236205867145</v>
+        <v>0.2245239696823652</v>
       </c>
       <c r="C28">
-        <v>2609.309493087947</v>
+        <v>2592.555888157717</v>
       </c>
       <c r="D28">
-        <v>3156.837493087946</v>
+        <v>3170.961888157717</v>
       </c>
       <c r="E28">
-        <v>137.728</v>
+        <v>168.606</v>
       </c>
       <c r="F28">
-        <v>802.828</v>
+        <v>833.706</v>
       </c>
       <c r="G28">
         <v>255.3</v>
@@ -3583,28 +3583,28 @@
         <v>214.4</v>
       </c>
       <c r="M28">
-        <v>44.3963884</v>
+        <v>46.1039418</v>
       </c>
       <c r="N28">
-        <v>170.0036116</v>
+        <v>168.2960582</v>
       </c>
       <c r="O28">
-        <v>59.50126406</v>
+        <v>58.90362037</v>
       </c>
       <c r="P28">
-        <v>110.50234754</v>
+        <v>109.39243783</v>
       </c>
       <c r="Q28">
-        <v>178.80234754</v>
+        <v>177.69243783</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2918620548469115</v>
+        <v>0.2942723557292674</v>
       </c>
       <c r="T28">
-        <v>1.208994456111019</v>
+        <v>1.220837161424281</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.829221649029451</v>
+        <v>4.650361587954286</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.2245239696823652</v>
+        <v>0.2241793187780159</v>
       </c>
       <c r="C29">
-        <v>2592.555888157717</v>
+        <v>2567.804578683825</v>
       </c>
       <c r="D29">
-        <v>3170.961888157717</v>
+        <v>3177.088578683824</v>
       </c>
       <c r="E29">
-        <v>168.606</v>
+        <v>199.484</v>
       </c>
       <c r="F29">
-        <v>833.706</v>
+        <v>864.5840000000001</v>
       </c>
       <c r="G29">
         <v>255.3</v>
@@ -3665,45 +3665,45 @@
         <v>214.4</v>
       </c>
       <c r="M29">
-        <v>46.1039418</v>
+        <v>49.97295520000001</v>
       </c>
       <c r="N29">
-        <v>168.2960582</v>
+        <v>164.4270448</v>
       </c>
       <c r="O29">
-        <v>58.90362037</v>
+        <v>57.54946568</v>
       </c>
       <c r="P29">
-        <v>109.39243783</v>
+        <v>106.87757912</v>
       </c>
       <c r="Q29">
-        <v>177.69243783</v>
+        <v>175.17757912</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2942723557292674</v>
+        <v>0.296749609413911</v>
       </c>
       <c r="T29">
-        <v>1.220837161424281</v>
+        <v>1.233008830774023</v>
       </c>
       <c r="U29">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V29">
         <v>0.35</v>
       </c>
       <c r="W29">
-        <v>0.035945</v>
+        <v>0.03757000000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.650361587954286</v>
+        <v>4.290320617260593</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2241793187780159</v>
+        <v>0.2233959178736666</v>
       </c>
       <c r="C30">
-        <v>2567.804578683825</v>
+        <v>2550.941169196593</v>
       </c>
       <c r="D30">
-        <v>3177.088578683824</v>
+        <v>3191.103169196593</v>
       </c>
       <c r="E30">
-        <v>199.484</v>
+        <v>230.362</v>
       </c>
       <c r="F30">
-        <v>864.5840000000001</v>
+        <v>895.462</v>
       </c>
       <c r="G30">
         <v>255.3</v>
@@ -3747,28 +3747,28 @@
         <v>214.4</v>
       </c>
       <c r="M30">
-        <v>49.97295520000001</v>
+        <v>51.75770360000001</v>
       </c>
       <c r="N30">
-        <v>164.4270448</v>
+        <v>162.6422964</v>
       </c>
       <c r="O30">
-        <v>57.54946568</v>
+        <v>56.92480373999999</v>
       </c>
       <c r="P30">
-        <v>106.87757912</v>
+        <v>105.71749266</v>
       </c>
       <c r="Q30">
-        <v>175.17757912</v>
+        <v>174.01749266</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.296749609413911</v>
+        <v>0.2992966448924882</v>
       </c>
       <c r="T30">
-        <v>1.233008830774023</v>
+        <v>1.24552336404911</v>
       </c>
       <c r="U30">
         <v>0.0578</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.290320617260593</v>
+        <v>4.142378527010228</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2233959178736666</v>
+        <v>0.2226125169693173</v>
       </c>
       <c r="C31">
-        <v>2550.941169196593</v>
+        <v>2534.201948234812</v>
       </c>
       <c r="D31">
-        <v>3191.103169196593</v>
+        <v>3205.241948234812</v>
       </c>
       <c r="E31">
-        <v>230.3619999999999</v>
+        <v>261.2399999999999</v>
       </c>
       <c r="F31">
-        <v>895.4619999999999</v>
+        <v>926.3399999999999</v>
       </c>
       <c r="G31">
         <v>255.3</v>
@@ -3829,28 +3829,28 @@
         <v>214.4</v>
       </c>
       <c r="M31">
-        <v>51.7577036</v>
+        <v>53.542452</v>
       </c>
       <c r="N31">
-        <v>162.6422964</v>
+        <v>160.857548</v>
       </c>
       <c r="O31">
-        <v>56.92480374</v>
+        <v>56.3001418</v>
       </c>
       <c r="P31">
-        <v>105.71749266</v>
+        <v>104.5574062</v>
       </c>
       <c r="Q31">
-        <v>174.01749266</v>
+        <v>172.8574062</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2992966448924882</v>
+        <v>0.3019164528133105</v>
       </c>
       <c r="T31">
-        <v>1.24552336404911</v>
+        <v>1.258395455417771</v>
       </c>
       <c r="U31">
         <v>0.0578</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.142378527010229</v>
+        <v>4.004299242776554</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2226125169693173</v>
+        <v>0.222534366064968</v>
       </c>
       <c r="C32">
-        <v>2534.201948234812</v>
+        <v>2504.741287502155</v>
       </c>
       <c r="D32">
-        <v>3205.241948234812</v>
+        <v>3206.659287502154</v>
       </c>
       <c r="E32">
-        <v>261.2399999999999</v>
+        <v>292.1179999999999</v>
       </c>
       <c r="F32">
-        <v>926.3399999999999</v>
+        <v>957.218</v>
       </c>
       <c r="G32">
         <v>255.3</v>
@@ -3911,45 +3911,45 @@
         <v>214.4</v>
       </c>
       <c r="M32">
-        <v>53.542452</v>
+        <v>58.6774634</v>
       </c>
       <c r="N32">
-        <v>160.857548</v>
+        <v>155.7225366</v>
       </c>
       <c r="O32">
-        <v>56.3001418</v>
+        <v>54.50288781</v>
       </c>
       <c r="P32">
-        <v>104.5574062</v>
+        <v>101.21964879</v>
       </c>
       <c r="Q32">
-        <v>172.8574062</v>
+        <v>169.51964879</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.3019164528133105</v>
+        <v>0.3046121971956059</v>
       </c>
       <c r="T32">
-        <v>1.258395455417771</v>
+        <v>1.271640650884074</v>
       </c>
       <c r="U32">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V32">
         <v>0.35</v>
       </c>
       <c r="W32">
-        <v>0.03757000000000001</v>
+        <v>0.039845</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.004299242776554</v>
+        <v>3.653873013195046</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.222534366064968</v>
+        <v>0.2217737151606188</v>
       </c>
       <c r="C33">
-        <v>2504.741287502155</v>
+        <v>2487.724154647866</v>
       </c>
       <c r="D33">
-        <v>3206.659287502154</v>
+        <v>3220.520154647866</v>
       </c>
       <c r="E33">
-        <v>292.1179999999999</v>
+        <v>322.9959999999999</v>
       </c>
       <c r="F33">
-        <v>957.218</v>
+        <v>988.0959999999999</v>
       </c>
       <c r="G33">
         <v>255.3</v>
@@ -3993,28 +3993,28 @@
         <v>214.4</v>
       </c>
       <c r="M33">
-        <v>58.6774634</v>
+        <v>60.5702848</v>
       </c>
       <c r="N33">
-        <v>155.7225366</v>
+        <v>153.8297152</v>
       </c>
       <c r="O33">
-        <v>54.50288781</v>
+        <v>53.84040032</v>
       </c>
       <c r="P33">
-        <v>101.21964879</v>
+        <v>99.98931488000001</v>
       </c>
       <c r="Q33">
-        <v>169.51964879</v>
+        <v>168.28931488</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.3046121971956059</v>
+        <v>0.3073872281773806</v>
       </c>
       <c r="T33">
-        <v>1.271640650884074</v>
+        <v>1.285275410922916</v>
       </c>
       <c r="U33">
         <v>0.0613</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.653873013195046</v>
+        <v>3.5396894815327</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2217737151606188</v>
+        <v>0.2216136642562694</v>
       </c>
       <c r="C34">
-        <v>2487.724154647866</v>
+        <v>2459.777935663904</v>
       </c>
       <c r="D34">
-        <v>3220.520154647866</v>
+        <v>3223.451935663904</v>
       </c>
       <c r="E34">
-        <v>322.9959999999999</v>
+        <v>353.8739999999999</v>
       </c>
       <c r="F34">
-        <v>988.0959999999999</v>
+        <v>1018.974</v>
       </c>
       <c r="G34">
         <v>255.3</v>
@@ -4075,45 +4075,45 @@
         <v>214.4</v>
       </c>
       <c r="M34">
-        <v>60.5702848</v>
+        <v>65.3162334</v>
       </c>
       <c r="N34">
-        <v>153.8297152</v>
+        <v>149.0837666</v>
       </c>
       <c r="O34">
-        <v>53.84040032</v>
+        <v>52.17931830999999</v>
       </c>
       <c r="P34">
-        <v>99.98931488000001</v>
+        <v>96.90444829</v>
       </c>
       <c r="Q34">
-        <v>168.28931488</v>
+        <v>165.20444829</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.3073872281773806</v>
+        <v>0.3102450959048798</v>
       </c>
       <c r="T34">
-        <v>1.285275410922916</v>
+        <v>1.299317178724111</v>
       </c>
       <c r="U34">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V34">
         <v>0.35</v>
       </c>
       <c r="W34">
-        <v>0.039845</v>
+        <v>0.04166500000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.5396894815327</v>
+        <v>3.282491791695998</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.2216136642562694</v>
+        <v>0.2208712133519202</v>
       </c>
       <c r="C35">
-        <v>2459.777935663904</v>
+        <v>2442.570114552474</v>
       </c>
       <c r="D35">
-        <v>3223.451935663904</v>
+        <v>3237.122114552474</v>
       </c>
       <c r="E35">
-        <v>353.8739999999999</v>
+        <v>384.7520000000001</v>
       </c>
       <c r="F35">
-        <v>1018.974</v>
+        <v>1049.852</v>
       </c>
       <c r="G35">
         <v>255.3</v>
@@ -4157,28 +4157,28 @@
         <v>214.4</v>
       </c>
       <c r="M35">
-        <v>65.3162334</v>
+        <v>67.29551320000002</v>
       </c>
       <c r="N35">
-        <v>149.0837666</v>
+        <v>147.1044868</v>
       </c>
       <c r="O35">
-        <v>52.17931830999999</v>
+        <v>51.48657038</v>
       </c>
       <c r="P35">
-        <v>96.90444829</v>
+        <v>95.61791642</v>
       </c>
       <c r="Q35">
-        <v>165.20444829</v>
+        <v>163.91791642</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.3102450959048798</v>
+        <v>0.3131895656847276</v>
       </c>
       <c r="T35">
-        <v>1.299317178724111</v>
+        <v>1.313784454640494</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.282491791695998</v>
+        <v>3.185947915469645</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.2208712133519202</v>
+        <v>0.2201287624475709</v>
       </c>
       <c r="C36">
-        <v>2442.570114552474</v>
+        <v>2425.478733626085</v>
       </c>
       <c r="D36">
-        <v>3237.122114552474</v>
+        <v>3250.908733626085</v>
       </c>
       <c r="E36">
-        <v>384.7520000000001</v>
+        <v>415.63</v>
       </c>
       <c r="F36">
-        <v>1049.852</v>
+        <v>1080.73</v>
       </c>
       <c r="G36">
         <v>255.3</v>
@@ -4239,28 +4239,28 @@
         <v>214.4</v>
       </c>
       <c r="M36">
-        <v>67.29551320000002</v>
+        <v>69.274793</v>
       </c>
       <c r="N36">
-        <v>147.1044868</v>
+        <v>145.125207</v>
       </c>
       <c r="O36">
-        <v>51.48657038</v>
+        <v>50.79382244999999</v>
       </c>
       <c r="P36">
-        <v>95.61791642</v>
+        <v>94.33138455</v>
       </c>
       <c r="Q36">
-        <v>163.91791642</v>
+        <v>162.63138455</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.3131895656847276</v>
+        <v>0.3162246345347245</v>
       </c>
       <c r="T36">
-        <v>1.313784454640494</v>
+        <v>1.32869687750815</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.185947915469645</v>
+        <v>3.094920832170512</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2201287624475709</v>
+        <v>0.2193863115432216</v>
       </c>
       <c r="C37">
-        <v>2425.478733626085</v>
+        <v>2408.505286973524</v>
       </c>
       <c r="D37">
-        <v>3250.908733626085</v>
+        <v>3264.813286973523</v>
       </c>
       <c r="E37">
-        <v>415.63</v>
+        <v>446.5079999999999</v>
       </c>
       <c r="F37">
-        <v>1080.73</v>
+        <v>1111.608</v>
       </c>
       <c r="G37">
         <v>255.3</v>
@@ -4321,28 +4321,28 @@
         <v>214.4</v>
       </c>
       <c r="M37">
-        <v>69.274793</v>
+        <v>71.2540728</v>
       </c>
       <c r="N37">
-        <v>145.125207</v>
+        <v>143.1459272</v>
       </c>
       <c r="O37">
-        <v>50.79382244999999</v>
+        <v>50.10107452</v>
       </c>
       <c r="P37">
-        <v>94.33138455</v>
+        <v>93.04485268000002</v>
       </c>
       <c r="Q37">
-        <v>162.63138455</v>
+        <v>161.34485268</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.3162246345347245</v>
+        <v>0.3193545492862838</v>
       </c>
       <c r="T37">
-        <v>1.32869687750815</v>
+        <v>1.34407531359042</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.094920832170512</v>
+        <v>3.008950809054665</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2193863115432216</v>
+        <v>0.2205197606388724</v>
       </c>
       <c r="C38">
-        <v>2408.505286973523</v>
+        <v>2356.447658212257</v>
       </c>
       <c r="D38">
-        <v>3264.813286973522</v>
+        <v>3243.633658212257</v>
       </c>
       <c r="E38">
-        <v>446.5079999999999</v>
+        <v>477.3859999999999</v>
       </c>
       <c r="F38">
-        <v>1111.608</v>
+        <v>1142.486</v>
       </c>
       <c r="G38">
         <v>255.3</v>
@@ -4403,45 +4403,45 @@
         <v>214.4</v>
       </c>
       <c r="M38">
-        <v>71.2540728</v>
+        <v>82.1447434</v>
       </c>
       <c r="N38">
-        <v>143.1459272</v>
+        <v>132.2552566</v>
       </c>
       <c r="O38">
-        <v>50.10107452</v>
+        <v>46.28933980999999</v>
       </c>
       <c r="P38">
-        <v>93.04485268000002</v>
+        <v>85.96591678999999</v>
       </c>
       <c r="Q38">
-        <v>161.34485268</v>
+        <v>154.26591679</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.3193545492862838</v>
+        <v>0.3225838264109085</v>
       </c>
       <c r="T38">
-        <v>1.34407531359042</v>
+        <v>1.359941953992762</v>
       </c>
       <c r="U38">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V38">
         <v>0.35</v>
       </c>
       <c r="W38">
-        <v>0.04166500000000001</v>
+        <v>0.04673500000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.008950809054665</v>
+        <v>2.610027022130792</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2205197606388724</v>
+        <v>0.2198280097345231</v>
       </c>
       <c r="C39">
-        <v>2356.447658212257</v>
+        <v>2338.462907522347</v>
       </c>
       <c r="D39">
-        <v>3243.633658212257</v>
+        <v>3256.526907522347</v>
       </c>
       <c r="E39">
-        <v>477.3859999999999</v>
+        <v>508.2639999999998</v>
       </c>
       <c r="F39">
-        <v>1142.486</v>
+        <v>1173.364</v>
       </c>
       <c r="G39">
         <v>255.3</v>
@@ -4485,28 +4485,28 @@
         <v>214.4</v>
       </c>
       <c r="M39">
-        <v>82.1447434</v>
+        <v>84.36487159999999</v>
       </c>
       <c r="N39">
-        <v>132.2552566</v>
+        <v>130.0351284</v>
       </c>
       <c r="O39">
-        <v>46.28933980999999</v>
+        <v>45.51229494</v>
       </c>
       <c r="P39">
-        <v>85.96591678999999</v>
+        <v>84.52283346000002</v>
       </c>
       <c r="Q39">
-        <v>154.26591679</v>
+        <v>152.82283346</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.3225838264109085</v>
+        <v>0.3259172737653598</v>
       </c>
       <c r="T39">
-        <v>1.359941953992762</v>
+        <v>1.376320421504857</v>
       </c>
       <c r="U39">
         <v>0.07190000000000001</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.610027022130792</v>
+        <v>2.541342100495771</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2198280097345231</v>
+        <v>0.2201249088301738</v>
       </c>
       <c r="C40">
-        <v>2338.462907522347</v>
+        <v>2302.038598046014</v>
       </c>
       <c r="D40">
-        <v>3256.526907522347</v>
+        <v>3250.980598046014</v>
       </c>
       <c r="E40">
-        <v>508.2639999999998</v>
+        <v>539.1419999999999</v>
       </c>
       <c r="F40">
-        <v>1173.364</v>
+        <v>1204.242</v>
       </c>
       <c r="G40">
         <v>255.3</v>
@@ -4567,45 +4567,45 @@
         <v>214.4</v>
       </c>
       <c r="M40">
-        <v>84.36487159999999</v>
+        <v>91.28154360000001</v>
       </c>
       <c r="N40">
-        <v>130.0351284</v>
+        <v>123.1184564</v>
       </c>
       <c r="O40">
-        <v>45.51229494</v>
+        <v>43.09145974</v>
       </c>
       <c r="P40">
-        <v>84.52283346000002</v>
+        <v>80.02699666000001</v>
       </c>
       <c r="Q40">
-        <v>152.82283346</v>
+        <v>148.32699666</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.3259172737653598</v>
+        <v>0.3293600144756948</v>
       </c>
       <c r="T40">
-        <v>1.376320421504857</v>
+        <v>1.393235887951776</v>
       </c>
       <c r="U40">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V40">
         <v>0.35</v>
       </c>
       <c r="W40">
-        <v>0.04673500000000001</v>
+        <v>0.04927000000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.541342100495771</v>
+        <v>2.348777108103154</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2201249088301738</v>
+        <v>0.2194585079258245</v>
       </c>
       <c r="C41">
-        <v>2302.038598046014</v>
+        <v>2283.635981120741</v>
       </c>
       <c r="D41">
-        <v>3250.980598046014</v>
+        <v>3263.45598112074</v>
       </c>
       <c r="E41">
-        <v>539.1419999999999</v>
+        <v>570.0199999999999</v>
       </c>
       <c r="F41">
-        <v>1204.242</v>
+        <v>1235.12</v>
       </c>
       <c r="G41">
         <v>255.3</v>
@@ -4649,28 +4649,28 @@
         <v>214.4</v>
       </c>
       <c r="M41">
-        <v>91.28154360000001</v>
+        <v>93.622096</v>
       </c>
       <c r="N41">
-        <v>123.1184564</v>
+        <v>120.777904</v>
       </c>
       <c r="O41">
-        <v>43.09145974</v>
+        <v>42.2722664</v>
       </c>
       <c r="P41">
-        <v>80.02699666000001</v>
+        <v>78.5056376</v>
       </c>
       <c r="Q41">
-        <v>148.32699666</v>
+        <v>146.8056376</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.3293600144756948</v>
+        <v>0.3329175132097075</v>
       </c>
       <c r="T41">
-        <v>1.393235887951776</v>
+        <v>1.410715203280257</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.348777108103154</v>
+        <v>2.290057680400576</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2194585079258245</v>
+        <v>0.2187921070214752</v>
       </c>
       <c r="C42">
-        <v>2283.635981120741</v>
+        <v>2265.329479639184</v>
       </c>
       <c r="D42">
-        <v>3263.45598112074</v>
+        <v>3276.027479639184</v>
       </c>
       <c r="E42">
-        <v>570.0199999999999</v>
+        <v>600.898</v>
       </c>
       <c r="F42">
-        <v>1235.12</v>
+        <v>1265.998</v>
       </c>
       <c r="G42">
         <v>255.3</v>
@@ -4731,28 +4731,28 @@
         <v>214.4</v>
       </c>
       <c r="M42">
-        <v>93.622096</v>
+        <v>95.96264840000001</v>
       </c>
       <c r="N42">
-        <v>120.777904</v>
+        <v>118.4373516</v>
       </c>
       <c r="O42">
-        <v>42.2722664</v>
+        <v>41.45307305999999</v>
       </c>
       <c r="P42">
-        <v>78.5056376</v>
+        <v>76.98427854000001</v>
       </c>
       <c r="Q42">
-        <v>146.8056376</v>
+        <v>145.28427854</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.3329175132097075</v>
+        <v>0.3365956051211444</v>
       </c>
       <c r="T42">
-        <v>1.410715203280257</v>
+        <v>1.428787037772417</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.290057680400576</v>
+        <v>2.234202615024952</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2187921070214752</v>
+        <v>0.2181257061171259</v>
       </c>
       <c r="C43">
-        <v>2265.329479639184</v>
+        <v>2247.120208665722</v>
       </c>
       <c r="D43">
-        <v>3276.027479639184</v>
+        <v>3288.696208665722</v>
       </c>
       <c r="E43">
-        <v>600.898</v>
+        <v>631.776</v>
       </c>
       <c r="F43">
-        <v>1265.998</v>
+        <v>1296.876</v>
       </c>
       <c r="G43">
         <v>255.3</v>
@@ -4813,28 +4813,28 @@
         <v>214.4</v>
       </c>
       <c r="M43">
-        <v>95.96264840000001</v>
+        <v>98.30320080000001</v>
       </c>
       <c r="N43">
-        <v>118.4373516</v>
+        <v>116.0967992</v>
       </c>
       <c r="O43">
-        <v>41.45307305999999</v>
+        <v>40.63387972</v>
       </c>
       <c r="P43">
-        <v>76.98427854000001</v>
+        <v>75.46291948</v>
       </c>
       <c r="Q43">
-        <v>145.28427854</v>
+        <v>143.76291948</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.3365956051211444</v>
+        <v>0.3404005277881482</v>
       </c>
       <c r="T43">
-        <v>1.428787037772417</v>
+        <v>1.447482038971202</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.234202615024952</v>
+        <v>2.181007314667215</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.218125706117126</v>
+        <v>0.2174593052127767</v>
       </c>
       <c r="C44">
-        <v>2247.120208665722</v>
+        <v>2229.009300579954</v>
       </c>
       <c r="D44">
-        <v>3288.696208665721</v>
+        <v>3301.463300579954</v>
       </c>
       <c r="E44">
-        <v>631.7759999999997</v>
+        <v>662.6539999999999</v>
       </c>
       <c r="F44">
-        <v>1296.876</v>
+        <v>1327.754</v>
       </c>
       <c r="G44">
         <v>255.3</v>
@@ -4895,28 +4895,28 @@
         <v>214.4</v>
       </c>
       <c r="M44">
-        <v>98.30320079999998</v>
+        <v>100.6437532</v>
       </c>
       <c r="N44">
-        <v>116.0967992</v>
+        <v>113.7562468</v>
       </c>
       <c r="O44">
-        <v>40.63387972</v>
+        <v>39.81468638</v>
       </c>
       <c r="P44">
-        <v>75.46291948000001</v>
+        <v>73.94156042</v>
       </c>
       <c r="Q44">
-        <v>143.76291948</v>
+        <v>142.24156042</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.3404005277881482</v>
+        <v>0.3443389565136433</v>
       </c>
       <c r="T44">
-        <v>1.447482038971202</v>
+        <v>1.466833005124331</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.181007314667215</v>
+        <v>2.130286214326117</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2174593052127767</v>
+        <v>0.2167929043084273</v>
       </c>
       <c r="C45">
-        <v>2229.009300579954</v>
+        <v>2210.997905414119</v>
       </c>
       <c r="D45">
-        <v>3301.463300579954</v>
+        <v>3314.329905414118</v>
       </c>
       <c r="E45">
-        <v>662.6539999999999</v>
+        <v>693.5319999999998</v>
       </c>
       <c r="F45">
-        <v>1327.754</v>
+        <v>1358.632</v>
       </c>
       <c r="G45">
         <v>255.3</v>
@@ -4977,28 +4977,28 @@
         <v>214.4</v>
       </c>
       <c r="M45">
-        <v>100.6437532</v>
+        <v>102.9843056</v>
       </c>
       <c r="N45">
-        <v>113.7562468</v>
+        <v>111.4156944</v>
       </c>
       <c r="O45">
-        <v>39.81468638</v>
+        <v>38.99549304</v>
       </c>
       <c r="P45">
-        <v>73.94156042</v>
+        <v>72.42020136000001</v>
       </c>
       <c r="Q45">
-        <v>142.24156042</v>
+        <v>140.72020136</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.3443389565136433</v>
+        <v>0.3484180434079059</v>
       </c>
       <c r="T45">
-        <v>1.466833005124331</v>
+        <v>1.4868750772115</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.130286214326117</v>
+        <v>2.081870618545978</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2167929043084273</v>
+        <v>0.2161265034040781</v>
       </c>
       <c r="C46">
-        <v>2210.997905414119</v>
+        <v>2193.08719119841</v>
       </c>
       <c r="D46">
-        <v>3314.329905414118</v>
+        <v>3327.297191198409</v>
       </c>
       <c r="E46">
-        <v>693.5319999999998</v>
+        <v>724.41</v>
       </c>
       <c r="F46">
-        <v>1358.632</v>
+        <v>1389.51</v>
       </c>
       <c r="G46">
         <v>255.3</v>
@@ -5059,28 +5059,28 @@
         <v>214.4</v>
       </c>
       <c r="M46">
-        <v>102.9843056</v>
+        <v>105.324858</v>
       </c>
       <c r="N46">
-        <v>111.4156944</v>
+        <v>109.075142</v>
       </c>
       <c r="O46">
-        <v>38.99549304</v>
+        <v>38.17629969999999</v>
       </c>
       <c r="P46">
-        <v>72.42020136000001</v>
+        <v>70.89884230000001</v>
       </c>
       <c r="Q46">
-        <v>140.72020136</v>
+        <v>139.1988423</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.3484180434079059</v>
+        <v>0.3526454607346874</v>
       </c>
       <c r="T46">
-        <v>1.4868750772115</v>
+        <v>1.507645951920021</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.081870618545978</v>
+        <v>2.035606827022733</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2161265034040781</v>
+        <v>0.2197059024997288</v>
       </c>
       <c r="C47">
-        <v>2193.08719119841</v>
+        <v>2093.725463010085</v>
       </c>
       <c r="D47">
-        <v>3327.297191198409</v>
+        <v>3258.813463010085</v>
       </c>
       <c r="E47">
-        <v>724.41</v>
+        <v>755.2879999999999</v>
       </c>
       <c r="F47">
-        <v>1389.51</v>
+        <v>1420.388</v>
       </c>
       <c r="G47">
         <v>255.3</v>
@@ -5141,45 +5141,45 @@
         <v>214.4</v>
       </c>
       <c r="M47">
-        <v>105.324858</v>
+        <v>127.83492</v>
       </c>
       <c r="N47">
-        <v>109.075142</v>
+        <v>86.56508000000002</v>
       </c>
       <c r="O47">
-        <v>38.17629969999999</v>
+        <v>30.297778</v>
       </c>
       <c r="P47">
-        <v>70.89884230000001</v>
+        <v>56.26730200000002</v>
       </c>
       <c r="Q47">
-        <v>139.1988423</v>
+        <v>124.567302</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.3526454607346874</v>
+        <v>0.3570294490735718</v>
       </c>
       <c r="T47">
-        <v>1.507645951920021</v>
+        <v>1.529186118284414</v>
       </c>
       <c r="U47">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V47">
         <v>0.35</v>
       </c>
       <c r="W47">
-        <v>0.04927000000000001</v>
+        <v>0.0585</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.035606827022733</v>
+        <v>1.677163016177427</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2197059024997288</v>
+        <v>0.2191318015953795</v>
       </c>
       <c r="C48">
-        <v>2093.725463010085</v>
+        <v>2073.64114160224</v>
       </c>
       <c r="D48">
-        <v>3258.813463010085</v>
+        <v>3269.60714160224</v>
       </c>
       <c r="E48">
-        <v>755.2879999999999</v>
+        <v>786.1659999999998</v>
       </c>
       <c r="F48">
-        <v>1420.388</v>
+        <v>1451.266</v>
       </c>
       <c r="G48">
         <v>255.3</v>
@@ -5223,28 +5223,28 @@
         <v>214.4</v>
       </c>
       <c r="M48">
-        <v>127.83492</v>
+        <v>130.61394</v>
       </c>
       <c r="N48">
-        <v>86.56508000000002</v>
+        <v>83.78606000000002</v>
       </c>
       <c r="O48">
-        <v>30.297778</v>
+        <v>29.32512100000001</v>
       </c>
       <c r="P48">
-        <v>56.26730200000002</v>
+        <v>54.46093900000001</v>
       </c>
       <c r="Q48">
-        <v>124.567302</v>
+        <v>122.760939</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.3570294490735718</v>
+        <v>0.3615788709346783</v>
       </c>
       <c r="T48">
-        <v>1.529186118284414</v>
+        <v>1.551539121115386</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.677163016177427</v>
+        <v>1.64147869668429</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2191318015953795</v>
+        <v>0.2185577006910302</v>
       </c>
       <c r="C49">
-        <v>2073.64114160224</v>
+        <v>2053.628558364286</v>
       </c>
       <c r="D49">
-        <v>3269.60714160224</v>
+        <v>3280.472558364285</v>
       </c>
       <c r="E49">
-        <v>786.1659999999998</v>
+        <v>817.044</v>
       </c>
       <c r="F49">
-        <v>1451.266</v>
+        <v>1482.144</v>
       </c>
       <c r="G49">
         <v>255.3</v>
@@ -5305,28 +5305,28 @@
         <v>214.4</v>
       </c>
       <c r="M49">
-        <v>130.61394</v>
+        <v>133.39296</v>
       </c>
       <c r="N49">
-        <v>83.78606000000002</v>
+        <v>81.00704000000002</v>
       </c>
       <c r="O49">
-        <v>29.32512100000001</v>
+        <v>28.352464</v>
       </c>
       <c r="P49">
-        <v>54.46093900000001</v>
+        <v>52.65457600000001</v>
       </c>
       <c r="Q49">
-        <v>122.760939</v>
+        <v>120.954576</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.3615788709346783</v>
+        <v>0.3663032705596735</v>
       </c>
       <c r="T49">
-        <v>1.551539121115386</v>
+        <v>1.574751854824473</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.64147869668429</v>
+        <v>1.6072812238367</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2185577006910302</v>
+        <v>0.2179835997866809</v>
       </c>
       <c r="C50">
-        <v>2053.628558364286</v>
+        <v>2033.688430872372</v>
       </c>
       <c r="D50">
-        <v>3280.472558364285</v>
+        <v>3291.410430872371</v>
       </c>
       <c r="E50">
-        <v>817.0439999999998</v>
+        <v>847.9219999999999</v>
       </c>
       <c r="F50">
-        <v>1482.144</v>
+        <v>1513.022</v>
       </c>
       <c r="G50">
         <v>255.3</v>
@@ -5387,28 +5387,28 @@
         <v>214.4</v>
       </c>
       <c r="M50">
-        <v>133.39296</v>
+        <v>136.17198</v>
       </c>
       <c r="N50">
-        <v>81.00704000000002</v>
+        <v>78.22802000000001</v>
       </c>
       <c r="O50">
-        <v>28.352464</v>
+        <v>27.379807</v>
       </c>
       <c r="P50">
-        <v>52.65457600000001</v>
+        <v>50.84821300000002</v>
       </c>
       <c r="Q50">
-        <v>120.954576</v>
+        <v>119.148213</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.3663032705596735</v>
+        <v>0.3712129407581979</v>
       </c>
       <c r="T50">
-        <v>1.574751854824473</v>
+        <v>1.59887489181627</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.6072812238367</v>
+        <v>1.57447956620738</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2179835997866809</v>
+        <v>0.2174094988823316</v>
       </c>
       <c r="C51">
-        <v>2033.688430872372</v>
+        <v>2013.82148630494</v>
       </c>
       <c r="D51">
-        <v>3291.410430872371</v>
+        <v>3302.421486304939</v>
       </c>
       <c r="E51">
-        <v>847.9219999999999</v>
+        <v>878.7999999999998</v>
       </c>
       <c r="F51">
-        <v>1513.022</v>
+        <v>1543.9</v>
       </c>
       <c r="G51">
         <v>255.3</v>
@@ -5469,28 +5469,28 @@
         <v>214.4</v>
       </c>
       <c r="M51">
-        <v>136.17198</v>
+        <v>138.951</v>
       </c>
       <c r="N51">
-        <v>78.22802000000001</v>
+        <v>75.44900000000001</v>
       </c>
       <c r="O51">
-        <v>27.379807</v>
+        <v>26.40715</v>
       </c>
       <c r="P51">
-        <v>50.84821300000002</v>
+        <v>49.04185000000001</v>
       </c>
       <c r="Q51">
-        <v>119.148213</v>
+        <v>117.34185</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.3712129407581979</v>
+        <v>0.3763189977646633</v>
       </c>
       <c r="T51">
-        <v>1.59887489181627</v>
+        <v>1.623962850287738</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.57447956620738</v>
+        <v>1.542989974883232</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2174094988823316</v>
+        <v>0.2168353979779823</v>
       </c>
       <c r="C52">
-        <v>2013.82148630494</v>
+        <v>1994.028461603878</v>
       </c>
       <c r="D52">
-        <v>3302.421486304939</v>
+        <v>3313.506461603878</v>
       </c>
       <c r="E52">
-        <v>878.7999999999998</v>
+        <v>909.6779999999998</v>
       </c>
       <c r="F52">
-        <v>1543.9</v>
+        <v>1574.778</v>
       </c>
       <c r="G52">
         <v>255.3</v>
@@ -5551,28 +5551,28 @@
         <v>214.4</v>
       </c>
       <c r="M52">
-        <v>138.951</v>
+        <v>141.73002</v>
       </c>
       <c r="N52">
-        <v>75.44900000000001</v>
+        <v>72.66998000000004</v>
       </c>
       <c r="O52">
-        <v>26.40715</v>
+        <v>25.43449300000001</v>
       </c>
       <c r="P52">
-        <v>49.04185000000001</v>
+        <v>47.23548700000003</v>
       </c>
       <c r="Q52">
-        <v>117.34185</v>
+        <v>115.535487</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3763189977646633</v>
+        <v>0.3816334652611885</v>
       </c>
       <c r="T52">
-        <v>1.623962850287738</v>
+        <v>1.650074807064164</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.542989974883232</v>
+        <v>1.512735269493365</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2168353979779823</v>
+        <v>0.2411712632994292</v>
       </c>
       <c r="C53">
-        <v>1994.028461603878</v>
+        <v>1550.412960553122</v>
       </c>
       <c r="D53">
-        <v>3313.506461603878</v>
+        <v>2900.768960553121</v>
       </c>
       <c r="E53">
-        <v>909.6779999999998</v>
+        <v>940.5559999999999</v>
       </c>
       <c r="F53">
-        <v>1574.778</v>
+        <v>1605.656</v>
       </c>
       <c r="G53">
         <v>255.3</v>
@@ -5633,45 +5633,45 @@
         <v>214.4</v>
       </c>
       <c r="M53">
-        <v>141.73002</v>
+        <v>235.7103008</v>
       </c>
       <c r="N53">
-        <v>72.66998000000004</v>
+        <v>-21.31030080000002</v>
       </c>
       <c r="O53">
-        <v>25.43449300000001</v>
+        <v>-7.458605280000007</v>
       </c>
       <c r="P53">
-        <v>47.23548700000003</v>
+        <v>-13.85169552000001</v>
       </c>
       <c r="Q53">
-        <v>115.535487</v>
+        <v>54.44830447999997</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3816334652611885</v>
+        <v>0.3940361570913334</v>
       </c>
       <c r="T53">
-        <v>1.650074807064164</v>
+        <v>1.711013848123656</v>
       </c>
       <c r="U53">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.35</v>
+        <v>0.3183568971967473</v>
       </c>
       <c r="W53">
-        <v>0.0585</v>
+        <v>0.1000652074915175</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.512735269493365</v>
+        <v>0.9095911348478496</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2411712632994292</v>
+        <v>0.2421812632994292</v>
       </c>
       <c r="C54">
-        <v>1550.412960553122</v>
+        <v>1504.616140901313</v>
       </c>
       <c r="D54">
-        <v>2900.768960553121</v>
+        <v>2885.850140901312</v>
       </c>
       <c r="E54">
-        <v>940.5559999999999</v>
+        <v>971.4339999999999</v>
       </c>
       <c r="F54">
-        <v>1605.656</v>
+        <v>1636.534</v>
       </c>
       <c r="G54">
         <v>255.3</v>
@@ -5715,37 +5715,37 @@
         <v>214.4</v>
       </c>
       <c r="M54">
-        <v>235.7103008</v>
+        <v>240.2431912</v>
       </c>
       <c r="N54">
-        <v>-21.31030080000002</v>
+        <v>-25.84319120000001</v>
       </c>
       <c r="O54">
-        <v>-7.458605280000007</v>
+        <v>-9.045116920000002</v>
       </c>
       <c r="P54">
-        <v>-13.85169552000001</v>
+        <v>-16.79807428000001</v>
       </c>
       <c r="Q54">
-        <v>54.44830447999997</v>
+        <v>51.50192571999997</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3940361570913334</v>
+        <v>0.401445437029447</v>
       </c>
       <c r="T54">
-        <v>1.711013848123656</v>
+        <v>1.747418398083734</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.3183568971967473</v>
+        <v>0.3123501632873747</v>
       </c>
       <c r="W54">
-        <v>0.1000652074915175</v>
+        <v>0.1009469960294134</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.9095911348478496</v>
+        <v>0.8924290379639279</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2421812632994292</v>
+        <v>0.2431912632994292</v>
       </c>
       <c r="C55">
-        <v>1504.616140901313</v>
+        <v>1458.971992726411</v>
       </c>
       <c r="D55">
-        <v>2885.850140901312</v>
+        <v>2871.083992726411</v>
       </c>
       <c r="E55">
-        <v>971.4339999999999</v>
+        <v>1002.312</v>
       </c>
       <c r="F55">
-        <v>1636.534</v>
+        <v>1667.412</v>
       </c>
       <c r="G55">
         <v>255.3</v>
@@ -5797,37 +5797,37 @@
         <v>214.4</v>
       </c>
       <c r="M55">
-        <v>240.2431912</v>
+        <v>244.7760816</v>
       </c>
       <c r="N55">
-        <v>-25.84319120000001</v>
+        <v>-30.37608160000002</v>
       </c>
       <c r="O55">
-        <v>-9.045116920000002</v>
+        <v>-10.63162856000001</v>
       </c>
       <c r="P55">
-        <v>-16.79807428000001</v>
+        <v>-19.74445304000001</v>
       </c>
       <c r="Q55">
-        <v>51.50192571999997</v>
+        <v>48.55554695999997</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.401445437029447</v>
+        <v>0.4091768595735654</v>
       </c>
       <c r="T55">
-        <v>1.747418398083734</v>
+        <v>1.785405754563815</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.3123501632873747</v>
+        <v>0.3065659010042752</v>
       </c>
       <c r="W55">
-        <v>0.1009469960294134</v>
+        <v>0.1017961257325724</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8924290379639279</v>
+        <v>0.8759025742979292</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2431912632994292</v>
+        <v>0.2442012632994291</v>
       </c>
       <c r="C56">
-        <v>1458.971992726411</v>
+        <v>1413.478184417382</v>
       </c>
       <c r="D56">
-        <v>2871.083992726411</v>
+        <v>2856.468184417382</v>
       </c>
       <c r="E56">
-        <v>1002.312</v>
+        <v>1033.19</v>
       </c>
       <c r="F56">
-        <v>1667.412</v>
+        <v>1698.29</v>
       </c>
       <c r="G56">
         <v>255.3</v>
@@ -5879,37 +5879,37 @@
         <v>214.4</v>
       </c>
       <c r="M56">
-        <v>244.7760816</v>
+        <v>249.308972</v>
       </c>
       <c r="N56">
-        <v>-30.37608160000002</v>
+        <v>-34.90897200000001</v>
       </c>
       <c r="O56">
-        <v>-10.63162856000001</v>
+        <v>-12.2181402</v>
       </c>
       <c r="P56">
-        <v>-19.74445304000001</v>
+        <v>-22.69083180000001</v>
       </c>
       <c r="Q56">
-        <v>48.55554695999997</v>
+        <v>45.60916819999998</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.4091768595735654</v>
+        <v>0.4172519008974224</v>
       </c>
       <c r="T56">
-        <v>1.785405754563815</v>
+        <v>1.825081437998566</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.3065659010042752</v>
+        <v>0.3009919755314702</v>
       </c>
       <c r="W56">
-        <v>0.1017961257325724</v>
+        <v>0.1026143779919802</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8759025742979292</v>
+        <v>0.8599770729470578</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2442012632994291</v>
+        <v>0.2452112632994292</v>
       </c>
       <c r="C57">
-        <v>1413.478184417382</v>
+        <v>1368.132431600784</v>
       </c>
       <c r="D57">
-        <v>2856.468184417382</v>
+        <v>2842.000431600784</v>
       </c>
       <c r="E57">
-        <v>1033.19</v>
+        <v>1064.068</v>
       </c>
       <c r="F57">
-        <v>1698.29</v>
+        <v>1729.168</v>
       </c>
       <c r="G57">
         <v>255.3</v>
@@ -5961,37 +5961,37 @@
         <v>214.4</v>
       </c>
       <c r="M57">
-        <v>249.308972</v>
+        <v>253.8418624000001</v>
       </c>
       <c r="N57">
-        <v>-34.90897200000001</v>
+        <v>-39.44186240000005</v>
       </c>
       <c r="O57">
-        <v>-12.2181402</v>
+        <v>-13.80465184000002</v>
       </c>
       <c r="P57">
-        <v>-22.69083180000001</v>
+        <v>-25.63721056000003</v>
       </c>
       <c r="Q57">
-        <v>45.60916819999998</v>
+        <v>42.66278943999995</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.4172519008974224</v>
+        <v>0.425693989554182</v>
       </c>
       <c r="T57">
-        <v>1.825081437998566</v>
+        <v>1.866560561589443</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.3009919755314702</v>
+        <v>0.2956171188255511</v>
       </c>
       <c r="W57">
-        <v>0.1026143779919802</v>
+        <v>0.1034034069564091</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8599770729470578</v>
+        <v>0.8446203395015746</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2452112632994292</v>
+        <v>0.2462212632994291</v>
       </c>
       <c r="C58">
-        <v>1368.132431600784</v>
+        <v>1322.932495950532</v>
       </c>
       <c r="D58">
-        <v>2842.000431600784</v>
+        <v>2827.678495950532</v>
       </c>
       <c r="E58">
-        <v>1064.068</v>
+        <v>1094.946</v>
       </c>
       <c r="F58">
-        <v>1729.168</v>
+        <v>1760.046</v>
       </c>
       <c r="G58">
         <v>255.3</v>
@@ -6043,37 +6043,37 @@
         <v>214.4</v>
       </c>
       <c r="M58">
-        <v>253.8418624000001</v>
+        <v>258.3747528</v>
       </c>
       <c r="N58">
-        <v>-39.44186240000005</v>
+        <v>-43.9747528</v>
       </c>
       <c r="O58">
-        <v>-13.80465184000002</v>
+        <v>-15.39116348</v>
       </c>
       <c r="P58">
-        <v>-25.63721056000003</v>
+        <v>-28.58358932</v>
       </c>
       <c r="Q58">
-        <v>42.66278943999995</v>
+        <v>39.71641067999998</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.425693989554182</v>
+        <v>0.4345287334973025</v>
       </c>
       <c r="T58">
-        <v>1.866560561589443</v>
+        <v>1.909968946742685</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2956171188255511</v>
+        <v>0.2904308535829976</v>
       </c>
       <c r="W58">
-        <v>0.1034034069564091</v>
+        <v>0.104164750694016</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8446203395015746</v>
+        <v>0.8298024388085645</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2462212632994291</v>
+        <v>0.2472312632994292</v>
       </c>
       <c r="C59">
-        <v>1322.932495950532</v>
+        <v>1277.876184033456</v>
       </c>
       <c r="D59">
-        <v>2827.678495950532</v>
+        <v>2813.500184033455</v>
       </c>
       <c r="E59">
-        <v>1094.946</v>
+        <v>1125.824</v>
       </c>
       <c r="F59">
-        <v>1760.046</v>
+        <v>1790.924</v>
       </c>
       <c r="G59">
         <v>255.3</v>
@@ -6125,37 +6125,37 @@
         <v>214.4</v>
       </c>
       <c r="M59">
-        <v>258.3747528</v>
+        <v>262.9076432</v>
       </c>
       <c r="N59">
-        <v>-43.9747528</v>
+        <v>-48.50764319999999</v>
       </c>
       <c r="O59">
-        <v>-15.39116348</v>
+        <v>-16.97767511999999</v>
       </c>
       <c r="P59">
-        <v>-28.58358932</v>
+        <v>-31.52996808</v>
       </c>
       <c r="Q59">
-        <v>39.71641067999998</v>
+        <v>36.77003191999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.4345287334973025</v>
+        <v>0.4437841795329526</v>
       </c>
       <c r="T59">
-        <v>1.909968946742685</v>
+        <v>1.955444397855607</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2904308535829976</v>
+        <v>0.2854234250729459</v>
       </c>
       <c r="W59">
-        <v>0.104164750694016</v>
+        <v>0.1048998411992915</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8298024388085645</v>
+        <v>0.815495500208417</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2472312632994292</v>
+        <v>0.2482412632994292</v>
       </c>
       <c r="C60">
-        <v>1277.876184033456</v>
+        <v>1232.961346189431</v>
       </c>
       <c r="D60">
-        <v>2813.500184033455</v>
+        <v>2799.46334618943</v>
       </c>
       <c r="E60">
-        <v>1125.824</v>
+        <v>1156.702</v>
       </c>
       <c r="F60">
-        <v>1790.924</v>
+        <v>1821.802</v>
       </c>
       <c r="G60">
         <v>255.3</v>
@@ -6207,37 +6207,37 @@
         <v>214.4</v>
       </c>
       <c r="M60">
-        <v>262.9076432</v>
+        <v>267.4405336</v>
       </c>
       <c r="N60">
-        <v>-48.50764319999999</v>
+        <v>-53.04053359999997</v>
       </c>
       <c r="O60">
-        <v>-16.97767511999999</v>
+        <v>-18.56418675999999</v>
       </c>
       <c r="P60">
-        <v>-31.52996808</v>
+        <v>-34.47634683999998</v>
       </c>
       <c r="Q60">
-        <v>36.77003191999999</v>
+        <v>33.82365316</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.4437841795329525</v>
+        <v>0.4534911107410733</v>
       </c>
       <c r="T60">
-        <v>1.955444397855606</v>
+        <v>2.003138163656963</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2854234250729459</v>
+        <v>0.280585739902218</v>
       </c>
       <c r="W60">
-        <v>0.1048998411992915</v>
+        <v>0.1056100133823544</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.815495500208417</v>
+        <v>0.8016735425777659</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2482412632994292</v>
+        <v>0.2905691128491383</v>
       </c>
       <c r="C61">
-        <v>1232.961346189431</v>
+        <v>717.972986192884</v>
       </c>
       <c r="D61">
-        <v>2799.46334618943</v>
+        <v>2315.352986192884</v>
       </c>
       <c r="E61">
-        <v>1156.702</v>
+        <v>1187.58</v>
       </c>
       <c r="F61">
-        <v>1821.802</v>
+        <v>1852.68</v>
       </c>
       <c r="G61">
         <v>255.3</v>
@@ -6289,45 +6289,45 @@
         <v>214.4</v>
       </c>
       <c r="M61">
-        <v>267.4405336</v>
+        <v>372.018144</v>
       </c>
       <c r="N61">
-        <v>-53.04053359999997</v>
+        <v>-157.618144</v>
       </c>
       <c r="O61">
-        <v>-18.56418675999999</v>
+        <v>-55.1663504</v>
       </c>
       <c r="P61">
-        <v>-34.47634683999998</v>
+        <v>-102.4517936</v>
       </c>
       <c r="Q61">
-        <v>33.82365316</v>
+        <v>-34.15179360000002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.4534911107410733</v>
+        <v>0.4859780123838731</v>
       </c>
       <c r="T61">
-        <v>2.003138163656963</v>
+        <v>2.162758402571106</v>
       </c>
       <c r="U61">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.280585739902218</v>
+        <v>0.2017105918360799</v>
       </c>
       <c r="W61">
-        <v>0.1056100133823544</v>
+        <v>0.1602965131593151</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.8016735425777659</v>
+        <v>0.5763159766745141</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2905691128491383</v>
+        <v>0.2921191128491384</v>
       </c>
       <c r="C62">
-        <v>717.972986192884</v>
+        <v>672.5252798997424</v>
       </c>
       <c r="D62">
-        <v>2315.352986192884</v>
+        <v>2300.783279899742</v>
       </c>
       <c r="E62">
-        <v>1187.58</v>
+        <v>1218.458</v>
       </c>
       <c r="F62">
-        <v>1852.68</v>
+        <v>1883.558</v>
       </c>
       <c r="G62">
         <v>255.3</v>
@@ -6371,37 +6371,37 @@
         <v>214.4</v>
       </c>
       <c r="M62">
-        <v>372.018144</v>
+        <v>378.2184463999999</v>
       </c>
       <c r="N62">
-        <v>-157.618144</v>
+        <v>-163.8184463999999</v>
       </c>
       <c r="O62">
-        <v>-55.1663504</v>
+        <v>-57.33645623999998</v>
       </c>
       <c r="P62">
-        <v>-102.4517936</v>
+        <v>-106.48199016</v>
       </c>
       <c r="Q62">
-        <v>-34.15179360000002</v>
+        <v>-38.18199015999998</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.4859780123838731</v>
+        <v>0.4972646280860238</v>
       </c>
       <c r="T62">
-        <v>2.162758402571106</v>
+        <v>2.218213746226775</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.2017105918360799</v>
+        <v>0.1984038608223737</v>
       </c>
       <c r="W62">
-        <v>0.1602965131593151</v>
+        <v>0.1609605047468673</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5763159766745141</v>
+        <v>0.5668681737782106</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2921191128491384</v>
+        <v>0.2936691128491384</v>
       </c>
       <c r="C63">
-        <v>672.5252798997424</v>
+        <v>627.2597911043342</v>
       </c>
       <c r="D63">
-        <v>2300.783279899742</v>
+        <v>2286.395791104334</v>
       </c>
       <c r="E63">
-        <v>1218.458</v>
+        <v>1249.336</v>
       </c>
       <c r="F63">
-        <v>1883.558</v>
+        <v>1914.436</v>
       </c>
       <c r="G63">
         <v>255.3</v>
@@ -6453,37 +6453,37 @@
         <v>214.4</v>
       </c>
       <c r="M63">
-        <v>378.2184463999999</v>
+        <v>384.4187488</v>
       </c>
       <c r="N63">
-        <v>-163.8184463999999</v>
+        <v>-170.0187488</v>
       </c>
       <c r="O63">
-        <v>-57.33645623999998</v>
+        <v>-59.50656207999999</v>
       </c>
       <c r="P63">
-        <v>-106.48199016</v>
+        <v>-110.51218672</v>
       </c>
       <c r="Q63">
-        <v>-38.18199015999998</v>
+        <v>-42.21218672000002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.4972646280860238</v>
+        <v>0.5091452761935508</v>
       </c>
       <c r="T63">
-        <v>2.218213746226775</v>
+        <v>2.276587792180112</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1984038608223737</v>
+        <v>0.1952037985510451</v>
       </c>
       <c r="W63">
-        <v>0.1609605047468673</v>
+        <v>0.1616030772509502</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5668681737782106</v>
+        <v>0.5577251387172717</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2936691128491384</v>
+        <v>0.2952191128491384</v>
       </c>
       <c r="C64">
-        <v>627.2597911043342</v>
+        <v>582.1731226677853</v>
       </c>
       <c r="D64">
-        <v>2286.395791104334</v>
+        <v>2272.187122667785</v>
       </c>
       <c r="E64">
-        <v>1249.336</v>
+        <v>1280.214</v>
       </c>
       <c r="F64">
-        <v>1914.436</v>
+        <v>1945.314</v>
       </c>
       <c r="G64">
         <v>255.3</v>
@@ -6535,37 +6535,37 @@
         <v>214.4</v>
       </c>
       <c r="M64">
-        <v>384.4187488</v>
+        <v>390.6190512</v>
       </c>
       <c r="N64">
-        <v>-170.0187488</v>
+        <v>-176.2190512</v>
       </c>
       <c r="O64">
-        <v>-59.50656207999999</v>
+        <v>-61.67666791999999</v>
       </c>
       <c r="P64">
-        <v>-110.51218672</v>
+        <v>-114.54238328</v>
       </c>
       <c r="Q64">
-        <v>-42.21218672000002</v>
+        <v>-46.24238328000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.5091452761935508</v>
+        <v>0.5216681214960792</v>
       </c>
       <c r="T64">
-        <v>2.276587792180112</v>
+        <v>2.338117191968764</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1952037985510451</v>
+        <v>0.1921053255581713</v>
       </c>
       <c r="W64">
-        <v>0.1616030772509502</v>
+        <v>0.1622252506279192</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5577251387172717</v>
+        <v>0.5488723587376324</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2952191128491384</v>
+        <v>0.2967691128491384</v>
       </c>
       <c r="C65">
-        <v>582.1731226677853</v>
+        <v>537.2619613749373</v>
       </c>
       <c r="D65">
-        <v>2272.187122667785</v>
+        <v>2258.153961374937</v>
       </c>
       <c r="E65">
-        <v>1280.214</v>
+        <v>1311.092</v>
       </c>
       <c r="F65">
-        <v>1945.314</v>
+        <v>1976.192</v>
       </c>
       <c r="G65">
         <v>255.3</v>
@@ -6617,37 +6617,37 @@
         <v>214.4</v>
       </c>
       <c r="M65">
-        <v>390.6190512</v>
+        <v>396.8193535999999</v>
       </c>
       <c r="N65">
-        <v>-176.2190512</v>
+        <v>-182.4193535999999</v>
       </c>
       <c r="O65">
-        <v>-61.67666791999999</v>
+        <v>-63.84677375999998</v>
       </c>
       <c r="P65">
-        <v>-114.54238328</v>
+        <v>-118.57257984</v>
       </c>
       <c r="Q65">
-        <v>-46.24238328000001</v>
+        <v>-50.27257983999998</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.5216681214960792</v>
+        <v>0.5348866804265258</v>
       </c>
       <c r="T65">
-        <v>2.338117191968764</v>
+        <v>2.403064891745673</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1921053255581713</v>
+        <v>0.189103679846325</v>
       </c>
       <c r="W65">
-        <v>0.1622252506279192</v>
+        <v>0.1628279810868579</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5488723587376324</v>
+        <v>0.540296228132357</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2967691128491384</v>
+        <v>0.2983191128491384</v>
       </c>
       <c r="C66">
-        <v>537.2619613749373</v>
+        <v>492.5230753586686</v>
       </c>
       <c r="D66">
-        <v>2258.153961374937</v>
+        <v>2244.293075358668</v>
       </c>
       <c r="E66">
-        <v>1311.092</v>
+        <v>1341.97</v>
       </c>
       <c r="F66">
-        <v>1976.192</v>
+        <v>2007.07</v>
       </c>
       <c r="G66">
         <v>255.3</v>
@@ -6699,37 +6699,37 @@
         <v>214.4</v>
       </c>
       <c r="M66">
-        <v>396.8193535999999</v>
+        <v>403.019656</v>
       </c>
       <c r="N66">
-        <v>-182.4193535999999</v>
+        <v>-188.619656</v>
       </c>
       <c r="O66">
-        <v>-63.84677375999998</v>
+        <v>-66.0168796</v>
       </c>
       <c r="P66">
-        <v>-118.57257984</v>
+        <v>-122.6027764</v>
       </c>
       <c r="Q66">
-        <v>-50.27257983999998</v>
+        <v>-54.30277640000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.5348866804265258</v>
+        <v>0.5488605855815695</v>
       </c>
       <c r="T66">
-        <v>2.403064891745673</v>
+        <v>2.471723888652693</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.189103679846325</v>
+        <v>0.1861943924640738</v>
       </c>
       <c r="W66">
-        <v>0.1628279810868579</v>
+        <v>0.163412165993214</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.540296228132357</v>
+        <v>0.5319839784687822</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2983191128491384</v>
+        <v>0.2998691128491384</v>
       </c>
       <c r="C67">
-        <v>492.5230753586686</v>
+        <v>447.9533116184948</v>
       </c>
       <c r="D67">
-        <v>2244.293075358668</v>
+        <v>2230.601311618494</v>
       </c>
       <c r="E67">
-        <v>1341.97</v>
+        <v>1372.848</v>
       </c>
       <c r="F67">
-        <v>2007.07</v>
+        <v>2037.948</v>
       </c>
       <c r="G67">
         <v>255.3</v>
@@ -6781,37 +6781,37 @@
         <v>214.4</v>
       </c>
       <c r="M67">
-        <v>403.019656</v>
+        <v>409.2199584</v>
       </c>
       <c r="N67">
-        <v>-188.619656</v>
+        <v>-194.8199584</v>
       </c>
       <c r="O67">
-        <v>-66.0168796</v>
+        <v>-68.18698543999999</v>
       </c>
       <c r="P67">
-        <v>-122.6027764</v>
+        <v>-126.63297296</v>
       </c>
       <c r="Q67">
-        <v>-54.30277640000001</v>
+        <v>-58.33297296000002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.5488605855815695</v>
+        <v>0.563656485157498</v>
       </c>
       <c r="T67">
-        <v>2.471723888652693</v>
+        <v>2.544421650083655</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1861943924640738</v>
+        <v>0.1833732653055272</v>
       </c>
       <c r="W67">
-        <v>0.163412165993214</v>
+        <v>0.1639786483266501</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5319839784687822</v>
+        <v>0.5239236151586492</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2998691128491384</v>
+        <v>0.3014191128491384</v>
       </c>
       <c r="C68">
-        <v>447.9533116184948</v>
+        <v>403.5495936294446</v>
       </c>
       <c r="D68">
-        <v>2230.601311618494</v>
+        <v>2217.075593629444</v>
       </c>
       <c r="E68">
-        <v>1372.848</v>
+        <v>1403.726</v>
       </c>
       <c r="F68">
-        <v>2037.948</v>
+        <v>2068.826</v>
       </c>
       <c r="G68">
         <v>255.3</v>
@@ -6863,37 +6863,37 @@
         <v>214.4</v>
       </c>
       <c r="M68">
-        <v>409.2199584</v>
+        <v>415.4202608</v>
       </c>
       <c r="N68">
-        <v>-194.8199584</v>
+        <v>-201.0202608</v>
       </c>
       <c r="O68">
-        <v>-68.18698543999999</v>
+        <v>-70.35709127999999</v>
       </c>
       <c r="P68">
-        <v>-126.63297296</v>
+        <v>-130.66316952</v>
       </c>
       <c r="Q68">
-        <v>-58.33297296000002</v>
+        <v>-62.36316952000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.563656485157498</v>
+        <v>0.5793491059198465</v>
       </c>
       <c r="T68">
-        <v>2.544421650083655</v>
+        <v>2.621525336449826</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1833732653055272</v>
+        <v>0.180636350897982</v>
       </c>
       <c r="W68">
-        <v>0.1639786483266501</v>
+        <v>0.1645282207396852</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5239236151586492</v>
+        <v>0.51610385970852</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.3014191128491384</v>
+        <v>0.3029691128491384</v>
       </c>
       <c r="C69">
-        <v>403.5495936294446</v>
+        <v>359.3089190374085</v>
       </c>
       <c r="D69">
-        <v>2217.075593629444</v>
+        <v>2203.712919037408</v>
       </c>
       <c r="E69">
-        <v>1403.726</v>
+        <v>1434.604</v>
       </c>
       <c r="F69">
-        <v>2068.826</v>
+        <v>2099.704</v>
       </c>
       <c r="G69">
         <v>255.3</v>
@@ -6945,37 +6945,37 @@
         <v>214.4</v>
       </c>
       <c r="M69">
-        <v>415.4202608</v>
+        <v>421.6205632</v>
       </c>
       <c r="N69">
-        <v>-201.0202608</v>
+        <v>-207.2205632</v>
       </c>
       <c r="O69">
-        <v>-70.35709127999999</v>
+        <v>-72.52719712000001</v>
       </c>
       <c r="P69">
-        <v>-130.66316952</v>
+        <v>-134.69336608</v>
       </c>
       <c r="Q69">
-        <v>-62.36316952000001</v>
+        <v>-66.39336608000005</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.5793491059198465</v>
+        <v>0.5960225154798415</v>
       </c>
       <c r="T69">
-        <v>2.621525336449826</v>
+        <v>2.703448003213883</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.180636350897982</v>
+        <v>0.1779799339730117</v>
       </c>
       <c r="W69">
-        <v>0.1645282207396852</v>
+        <v>0.1650616292582193</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.51610385970852</v>
+        <v>0.5085140970657476</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.3029691128491384</v>
+        <v>0.3045191128491384</v>
       </c>
       <c r="C70">
-        <v>359.3089190374085</v>
+        <v>315.2283574373314</v>
       </c>
       <c r="D70">
-        <v>2203.712919037408</v>
+        <v>2190.510357437331</v>
       </c>
       <c r="E70">
-        <v>1434.604</v>
+        <v>1465.482</v>
       </c>
       <c r="F70">
-        <v>2099.704</v>
+        <v>2130.582</v>
       </c>
       <c r="G70">
         <v>255.3</v>
@@ -7027,37 +7027,37 @@
         <v>214.4</v>
       </c>
       <c r="M70">
-        <v>421.6205632</v>
+        <v>427.8208656</v>
       </c>
       <c r="N70">
-        <v>-207.2205632</v>
+        <v>-213.4208656</v>
       </c>
       <c r="O70">
-        <v>-72.52719712000001</v>
+        <v>-74.69730295999999</v>
       </c>
       <c r="P70">
-        <v>-134.69336608</v>
+        <v>-138.72356264</v>
       </c>
       <c r="Q70">
-        <v>-66.39336608000005</v>
+        <v>-70.42356264000003</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.5960225154798415</v>
+        <v>0.6137716288824172</v>
       </c>
       <c r="T70">
-        <v>2.703448003213883</v>
+        <v>2.790656003317557</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1779799339730117</v>
+        <v>0.1754005146400695</v>
       </c>
       <c r="W70">
-        <v>0.1650616292582193</v>
+        <v>0.1655795766602741</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5085140970657476</v>
+        <v>0.5011443275430557</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.3045191128491384</v>
+        <v>0.3341675728581233</v>
       </c>
       <c r="C71">
-        <v>315.2283574373314</v>
+        <v>59.13342999972065</v>
       </c>
       <c r="D71">
-        <v>2190.510357437331</v>
+        <v>1965.293429999721</v>
       </c>
       <c r="E71">
-        <v>1465.482</v>
+        <v>1496.36</v>
       </c>
       <c r="F71">
-        <v>2130.582</v>
+        <v>2161.46</v>
       </c>
       <c r="G71">
         <v>255.3</v>
@@ -7109,45 +7109,45 @@
         <v>214.4</v>
       </c>
       <c r="M71">
-        <v>427.8208656</v>
+        <v>509.672268</v>
       </c>
       <c r="N71">
-        <v>-213.4208656</v>
+        <v>-295.2722680000001</v>
       </c>
       <c r="O71">
-        <v>-74.69730295999999</v>
+        <v>-103.3452938</v>
       </c>
       <c r="P71">
-        <v>-138.72356264</v>
+        <v>-191.9269742</v>
       </c>
       <c r="Q71">
-        <v>-70.42356264000003</v>
+        <v>-123.6269742000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.6137716288824172</v>
+        <v>0.6446988832084474</v>
       </c>
       <c r="T71">
-        <v>2.790656003317557</v>
+        <v>2.942613114486806</v>
       </c>
       <c r="U71">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.1754005146400695</v>
+        <v>0.1472318678323695</v>
       </c>
       <c r="W71">
-        <v>0.1655795766602741</v>
+        <v>0.2010827255651273</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.5011443275430557</v>
+        <v>0.4206624795210556</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.3341675728581233</v>
+        <v>0.3360675728581233</v>
       </c>
       <c r="C72">
-        <v>59.13342999972065</v>
+        <v>15.39123893548231</v>
       </c>
       <c r="D72">
-        <v>1965.293429999721</v>
+        <v>1952.429238935483</v>
       </c>
       <c r="E72">
-        <v>1496.36</v>
+        <v>1527.238</v>
       </c>
       <c r="F72">
-        <v>2161.46</v>
+        <v>2192.338</v>
       </c>
       <c r="G72">
         <v>255.3</v>
@@ -7191,37 +7191,37 @@
         <v>214.4</v>
       </c>
       <c r="M72">
-        <v>509.672268</v>
+        <v>516.9533004000001</v>
       </c>
       <c r="N72">
-        <v>-295.2722680000001</v>
+        <v>-302.5533004000001</v>
       </c>
       <c r="O72">
-        <v>-103.3452938</v>
+        <v>-105.89365514</v>
       </c>
       <c r="P72">
-        <v>-191.9269742</v>
+        <v>-196.6596452600001</v>
       </c>
       <c r="Q72">
-        <v>-123.6269742000001</v>
+        <v>-128.3596452600001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.6446988832084474</v>
+        <v>0.6653505688363249</v>
       </c>
       <c r="T72">
-        <v>2.942613114486806</v>
+        <v>3.044082532227731</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.1472318678323695</v>
+        <v>0.1451581795530403</v>
       </c>
       <c r="W72">
-        <v>0.2010827255651273</v>
+        <v>0.2015717012613931</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4206624795210556</v>
+        <v>0.4147376558658294</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.3360675728581233</v>
+        <v>0.3379675728581232</v>
       </c>
       <c r="C73">
-        <v>15.39123893548276</v>
+        <v>-28.18363744161888</v>
       </c>
       <c r="D73">
-        <v>1952.429238935483</v>
+        <v>1939.732362558381</v>
       </c>
       <c r="E73">
-        <v>1527.238</v>
+        <v>1558.116</v>
       </c>
       <c r="F73">
-        <v>2192.338</v>
+        <v>2223.216</v>
       </c>
       <c r="G73">
         <v>255.3</v>
@@ -7273,37 +7273,37 @@
         <v>214.4</v>
       </c>
       <c r="M73">
-        <v>516.9533004</v>
+        <v>524.2343327999999</v>
       </c>
       <c r="N73">
-        <v>-302.5533004</v>
+        <v>-309.8343328</v>
       </c>
       <c r="O73">
-        <v>-105.89365514</v>
+        <v>-108.44201648</v>
       </c>
       <c r="P73">
-        <v>-196.65964526</v>
+        <v>-201.39231632</v>
       </c>
       <c r="Q73">
-        <v>-128.35964526</v>
+        <v>-133.09231632</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.6653505688363246</v>
+        <v>0.6874773748661933</v>
       </c>
       <c r="T73">
-        <v>3.044082532227729</v>
+        <v>3.152799765521577</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.1451581795530403</v>
+        <v>0.1431420937259148</v>
       </c>
       <c r="W73">
-        <v>0.2015717012613931</v>
+        <v>0.2020470942994293</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4147376558658296</v>
+        <v>0.4089774106454708</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.3379675728581232</v>
+        <v>0.3398675728581232</v>
       </c>
       <c r="C74">
-        <v>-28.18363744161888</v>
+        <v>-71.59444224236722</v>
       </c>
       <c r="D74">
-        <v>1939.732362558381</v>
+        <v>1927.199557757632</v>
       </c>
       <c r="E74">
-        <v>1558.116</v>
+        <v>1588.994</v>
       </c>
       <c r="F74">
-        <v>2223.216</v>
+        <v>2254.094</v>
       </c>
       <c r="G74">
         <v>255.3</v>
@@ -7355,37 +7355,37 @@
         <v>214.4</v>
       </c>
       <c r="M74">
-        <v>524.2343327999999</v>
+        <v>531.5153651999999</v>
       </c>
       <c r="N74">
-        <v>-309.8343328</v>
+        <v>-317.1153651999999</v>
       </c>
       <c r="O74">
-        <v>-108.44201648</v>
+        <v>-110.99037782</v>
       </c>
       <c r="P74">
-        <v>-201.39231632</v>
+        <v>-206.12498738</v>
       </c>
       <c r="Q74">
-        <v>-133.09231632</v>
+        <v>-137.82498738</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.6874773748661933</v>
+        <v>0.7112432035649412</v>
       </c>
       <c r="T74">
-        <v>3.152799765521577</v>
+        <v>3.269570127207561</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.1431420937259148</v>
+        <v>0.1411812431269297</v>
       </c>
       <c r="W74">
-        <v>0.2020470942994293</v>
+        <v>0.20250946287067</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4089774106454708</v>
+        <v>0.4033749803626562</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.3398675728581232</v>
+        <v>0.3417675728581233</v>
       </c>
       <c r="C75">
-        <v>-71.59444224236722</v>
+        <v>-114.8443352993645</v>
       </c>
       <c r="D75">
-        <v>1927.199557757632</v>
+        <v>1914.827664700635</v>
       </c>
       <c r="E75">
-        <v>1588.994</v>
+        <v>1619.872</v>
       </c>
       <c r="F75">
-        <v>2254.094</v>
+        <v>2284.972</v>
       </c>
       <c r="G75">
         <v>255.3</v>
@@ -7437,37 +7437,37 @@
         <v>214.4</v>
       </c>
       <c r="M75">
-        <v>531.5153651999999</v>
+        <v>538.7963976</v>
       </c>
       <c r="N75">
-        <v>-317.1153651999999</v>
+        <v>-324.3963976</v>
       </c>
       <c r="O75">
-        <v>-110.99037782</v>
+        <v>-113.53873916</v>
       </c>
       <c r="P75">
-        <v>-206.12498738</v>
+        <v>-210.85765844</v>
       </c>
       <c r="Q75">
-        <v>-137.82498738</v>
+        <v>-142.55765844</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.7112432035649412</v>
+        <v>0.7368371729328237</v>
       </c>
       <c r="T75">
-        <v>3.269570127207561</v>
+        <v>3.395322824407852</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1411812431269297</v>
+        <v>0.1392733884900793</v>
       </c>
       <c r="W75">
-        <v>0.20250946287067</v>
+        <v>0.2029593349940393</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4033749803626562</v>
+        <v>0.3979239671145121</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.3417675728581233</v>
+        <v>0.3436675728581232</v>
       </c>
       <c r="C76">
-        <v>-114.8443352993645</v>
+        <v>-157.9363958230456</v>
       </c>
       <c r="D76">
-        <v>1914.827664700635</v>
+        <v>1902.613604176954</v>
       </c>
       <c r="E76">
-        <v>1619.872</v>
+        <v>1650.75</v>
       </c>
       <c r="F76">
-        <v>2284.972</v>
+        <v>2315.85</v>
       </c>
       <c r="G76">
         <v>255.3</v>
@@ -7519,37 +7519,37 @@
         <v>214.4</v>
       </c>
       <c r="M76">
-        <v>538.7963976</v>
+        <v>546.07743</v>
       </c>
       <c r="N76">
-        <v>-324.3963976</v>
+        <v>-331.6774300000001</v>
       </c>
       <c r="O76">
-        <v>-113.53873916</v>
+        <v>-116.0871005</v>
       </c>
       <c r="P76">
-        <v>-210.85765844</v>
+        <v>-215.5903295000001</v>
       </c>
       <c r="Q76">
-        <v>-142.55765844</v>
+        <v>-147.2903295000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.7368371729328237</v>
+        <v>0.7644786598501365</v>
       </c>
       <c r="T76">
-        <v>3.395322824407852</v>
+        <v>3.531135737384166</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1392733884900793</v>
+        <v>0.1374164099768782</v>
       </c>
       <c r="W76">
-        <v>0.2029593349940393</v>
+        <v>0.2033972105274521</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3979239671145121</v>
+        <v>0.3926183142196519</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.3436675728581232</v>
+        <v>0.3455675728581232</v>
       </c>
       <c r="C77">
-        <v>-157.9363958230456</v>
+        <v>-200.8736249567019</v>
       </c>
       <c r="D77">
-        <v>1902.613604176954</v>
+        <v>1890.554375043298</v>
       </c>
       <c r="E77">
-        <v>1650.75</v>
+        <v>1681.628</v>
       </c>
       <c r="F77">
-        <v>2315.85</v>
+        <v>2346.728</v>
       </c>
       <c r="G77">
         <v>255.3</v>
@@ -7601,37 +7601,37 @@
         <v>214.4</v>
       </c>
       <c r="M77">
-        <v>546.07743</v>
+        <v>553.3584623999999</v>
       </c>
       <c r="N77">
-        <v>-331.6774300000001</v>
+        <v>-338.9584623999999</v>
       </c>
       <c r="O77">
-        <v>-116.0871005</v>
+        <v>-118.63546184</v>
       </c>
       <c r="P77">
-        <v>-215.5903295000001</v>
+        <v>-220.32300056</v>
       </c>
       <c r="Q77">
-        <v>-147.2903295000001</v>
+        <v>-152.02300056</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.7644786598501365</v>
+        <v>0.794423604010559</v>
       </c>
       <c r="T77">
-        <v>3.531135737384166</v>
+        <v>3.678266393108507</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1374164099768782</v>
+        <v>0.1356082993192877</v>
       </c>
       <c r="W77">
-        <v>0.2033972105274521</v>
+        <v>0.203823563020512</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3926183142196519</v>
+        <v>0.3874522837693934</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.3455675728581232</v>
+        <v>0.3474675728581233</v>
       </c>
       <c r="C78">
-        <v>-200.8736249567019</v>
+        <v>-243.6589482349377</v>
       </c>
       <c r="D78">
-        <v>1890.554375043298</v>
+        <v>1878.647051765062</v>
       </c>
       <c r="E78">
-        <v>1681.628</v>
+        <v>1712.506</v>
       </c>
       <c r="F78">
-        <v>2346.728</v>
+        <v>2377.606</v>
       </c>
       <c r="G78">
         <v>255.3</v>
@@ -7683,37 +7683,37 @@
         <v>214.4</v>
       </c>
       <c r="M78">
-        <v>553.3584623999999</v>
+        <v>560.6394948</v>
       </c>
       <c r="N78">
-        <v>-338.9584623999999</v>
+        <v>-346.2394948</v>
       </c>
       <c r="O78">
-        <v>-118.63546184</v>
+        <v>-121.18382318</v>
       </c>
       <c r="P78">
-        <v>-220.32300056</v>
+        <v>-225.05567162</v>
       </c>
       <c r="Q78">
-        <v>-152.02300056</v>
+        <v>-156.75567162</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.794423604010559</v>
+        <v>0.8269724563588443</v>
       </c>
       <c r="T78">
-        <v>3.678266393108507</v>
+        <v>3.838191018895833</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1356082993192877</v>
+        <v>0.1338471525748813</v>
       </c>
       <c r="W78">
-        <v>0.203823563020512</v>
+        <v>0.204238841422843</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3874522837693934</v>
+        <v>0.3824204359282324</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.3474675728581233</v>
+        <v>0.3493675728581233</v>
       </c>
       <c r="C79">
-        <v>-243.6589482349377</v>
+        <v>-286.2952179498052</v>
       </c>
       <c r="D79">
-        <v>1878.647051765062</v>
+        <v>1866.888782050195</v>
       </c>
       <c r="E79">
-        <v>1712.506</v>
+        <v>1743.384</v>
       </c>
       <c r="F79">
-        <v>2377.606</v>
+        <v>2408.484</v>
       </c>
       <c r="G79">
         <v>255.3</v>
@@ -7765,37 +7765,37 @@
         <v>214.4</v>
       </c>
       <c r="M79">
-        <v>560.6394948</v>
+        <v>567.9205272</v>
       </c>
       <c r="N79">
-        <v>-346.2394948</v>
+        <v>-353.5205272000001</v>
       </c>
       <c r="O79">
-        <v>-121.18382318</v>
+        <v>-123.73218452</v>
       </c>
       <c r="P79">
-        <v>-225.05567162</v>
+        <v>-229.78834268</v>
       </c>
       <c r="Q79">
-        <v>-156.75567162</v>
+        <v>-161.48834268</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.8269724563588443</v>
+        <v>0.8624802952842462</v>
       </c>
       <c r="T79">
-        <v>3.838191018895833</v>
+        <v>4.012654247027462</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1338471525748813</v>
+        <v>0.1321311634393059</v>
       </c>
       <c r="W79">
-        <v>0.204238841422843</v>
+        <v>0.2046434716610117</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3824204359282324</v>
+        <v>0.3775176098265883</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.3493675728581233</v>
+        <v>0.3512675728581233</v>
       </c>
       <c r="C80">
-        <v>-286.2952179498052</v>
+        <v>-328.7852154286443</v>
       </c>
       <c r="D80">
-        <v>1866.888782050195</v>
+        <v>1855.276784571356</v>
       </c>
       <c r="E80">
-        <v>1743.384</v>
+        <v>1774.262</v>
       </c>
       <c r="F80">
-        <v>2408.484</v>
+        <v>2439.362</v>
       </c>
       <c r="G80">
         <v>255.3</v>
@@ -7847,37 +7847,37 @@
         <v>214.4</v>
       </c>
       <c r="M80">
-        <v>567.9205272</v>
+        <v>575.2015596</v>
       </c>
       <c r="N80">
-        <v>-353.5205272000001</v>
+        <v>-360.8015596</v>
       </c>
       <c r="O80">
-        <v>-123.73218452</v>
+        <v>-126.28054586</v>
       </c>
       <c r="P80">
-        <v>-229.78834268</v>
+        <v>-234.52101374</v>
       </c>
       <c r="Q80">
-        <v>-161.48834268</v>
+        <v>-166.22101374</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.8624802952842462</v>
+        <v>0.9013698331549248</v>
       </c>
       <c r="T80">
-        <v>4.012654247027462</v>
+        <v>4.203733020695437</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1321311634393059</v>
+        <v>0.1304586170666565</v>
       </c>
       <c r="W80">
-        <v>0.2046434716610117</v>
+        <v>0.2050378580956824</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3775176098265883</v>
+        <v>0.3727389059047328</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.3512675728581233</v>
+        <v>0.3531675728581233</v>
       </c>
       <c r="C81">
-        <v>-328.7852154286443</v>
+        <v>-371.1316532274245</v>
       </c>
       <c r="D81">
-        <v>1855.276784571356</v>
+        <v>1843.808346772575</v>
       </c>
       <c r="E81">
-        <v>1774.262</v>
+        <v>1805.14</v>
       </c>
       <c r="F81">
-        <v>2439.362</v>
+        <v>2470.24</v>
       </c>
       <c r="G81">
         <v>255.3</v>
@@ -7929,37 +7929,37 @@
         <v>214.4</v>
       </c>
       <c r="M81">
-        <v>575.2015596</v>
+        <v>582.482592</v>
       </c>
       <c r="N81">
-        <v>-360.8015596</v>
+        <v>-368.082592</v>
       </c>
       <c r="O81">
-        <v>-126.28054586</v>
+        <v>-128.8289072</v>
       </c>
       <c r="P81">
-        <v>-234.52101374</v>
+        <v>-239.2536848</v>
       </c>
       <c r="Q81">
-        <v>-166.22101374</v>
+        <v>-170.9536848</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.9013698331549248</v>
+        <v>0.9441483248126711</v>
       </c>
       <c r="T81">
-        <v>4.203733020695437</v>
+        <v>4.413919671730209</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1304586170666565</v>
+        <v>0.1288278843533233</v>
       </c>
       <c r="W81">
-        <v>0.2050378580956824</v>
+        <v>0.2054223848694864</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3727389059047328</v>
+        <v>0.3680796695809238</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.3531675728581233</v>
+        <v>0.3550675728581233</v>
       </c>
       <c r="C82">
-        <v>-371.1316532274245</v>
+        <v>-413.3371772432552</v>
       </c>
       <c r="D82">
-        <v>1843.808346772575</v>
+        <v>1832.480822756745</v>
       </c>
       <c r="E82">
-        <v>1805.14</v>
+        <v>1836.018</v>
       </c>
       <c r="F82">
-        <v>2470.24</v>
+        <v>2501.118</v>
       </c>
       <c r="G82">
         <v>255.3</v>
@@ -8011,37 +8011,37 @@
         <v>214.4</v>
       </c>
       <c r="M82">
-        <v>582.482592</v>
+        <v>589.7636244</v>
       </c>
       <c r="N82">
-        <v>-368.082592</v>
+        <v>-375.3636244</v>
       </c>
       <c r="O82">
-        <v>-128.8289072</v>
+        <v>-131.37726854</v>
       </c>
       <c r="P82">
-        <v>-239.2536848</v>
+        <v>-243.98635586</v>
       </c>
       <c r="Q82">
-        <v>-170.9536848</v>
+        <v>-175.68635586</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.9441483248126711</v>
+        <v>0.9914298155922854</v>
       </c>
       <c r="T82">
-        <v>4.413919671730209</v>
+        <v>4.64623123340022</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1288278843533233</v>
+        <v>0.1272374166452576</v>
       </c>
       <c r="W82">
-        <v>0.2054223848694864</v>
+        <v>0.2057974171550483</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3680796695809238</v>
+        <v>0.3635354761293074</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3550675728581233</v>
+        <v>0.3569675728581233</v>
       </c>
       <c r="C83">
-        <v>-413.3371772432552</v>
+        <v>-455.4043687494832</v>
       </c>
       <c r="D83">
-        <v>1832.480822756745</v>
+        <v>1821.291631250517</v>
       </c>
       <c r="E83">
-        <v>1836.018</v>
+        <v>1866.896</v>
       </c>
       <c r="F83">
-        <v>2501.118</v>
+        <v>2531.996</v>
       </c>
       <c r="G83">
         <v>255.3</v>
@@ -8093,37 +8093,37 @@
         <v>214.4</v>
       </c>
       <c r="M83">
-        <v>589.7636244</v>
+        <v>597.0446568000001</v>
       </c>
       <c r="N83">
-        <v>-375.3636244</v>
+        <v>-382.6446568000001</v>
       </c>
       <c r="O83">
-        <v>-131.37726854</v>
+        <v>-133.92562988</v>
       </c>
       <c r="P83">
-        <v>-243.98635586</v>
+        <v>-248.7190269200001</v>
       </c>
       <c r="Q83">
-        <v>-175.68635586</v>
+        <v>-180.4190269200001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.9914298155922854</v>
+        <v>1.043964805347412</v>
       </c>
       <c r="T83">
-        <v>4.64623123340022</v>
+        <v>4.904355190811344</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1272374166452576</v>
+        <v>0.1256857408325105</v>
       </c>
       <c r="W83">
-        <v>0.2057974171550483</v>
+        <v>0.206163302311694</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3635354761293074</v>
+        <v>0.3591021166643157</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3569675728581233</v>
+        <v>0.3588675728581233</v>
       </c>
       <c r="C84">
-        <v>-455.4043687494832</v>
+        <v>-497.3357463567008</v>
       </c>
       <c r="D84">
-        <v>1821.291631250517</v>
+        <v>1810.238253643299</v>
       </c>
       <c r="E84">
-        <v>1866.896</v>
+        <v>1897.774</v>
       </c>
       <c r="F84">
-        <v>2531.996</v>
+        <v>2562.874</v>
       </c>
       <c r="G84">
         <v>255.3</v>
@@ -8175,37 +8175,37 @@
         <v>214.4</v>
       </c>
       <c r="M84">
-        <v>597.0446568000001</v>
+        <v>604.3256891999999</v>
       </c>
       <c r="N84">
-        <v>-382.6446568000001</v>
+        <v>-389.9256892</v>
       </c>
       <c r="O84">
-        <v>-133.92562988</v>
+        <v>-136.47399122</v>
       </c>
       <c r="P84">
-        <v>-248.7190269200001</v>
+        <v>-253.45169798</v>
       </c>
       <c r="Q84">
-        <v>-180.4190269200001</v>
+        <v>-185.15169798</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>1.043964805347412</v>
+        <v>1.102680382132555</v>
       </c>
       <c r="T84">
-        <v>4.904355190811344</v>
+        <v>5.192846672623777</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1256857408325105</v>
+        <v>0.1241714547983839</v>
       </c>
       <c r="W84">
-        <v>0.206163302311694</v>
+        <v>0.2065203709585411</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3591021166643157</v>
+        <v>0.3547755851382397</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3588675728581233</v>
+        <v>0.3607675728581232</v>
       </c>
       <c r="C85">
-        <v>-497.3357463567008</v>
+        <v>-539.1337679027647</v>
       </c>
       <c r="D85">
-        <v>1810.238253643299</v>
+        <v>1799.318232097235</v>
       </c>
       <c r="E85">
-        <v>1897.774</v>
+        <v>1928.652</v>
       </c>
       <c r="F85">
-        <v>2562.874</v>
+        <v>2593.752</v>
       </c>
       <c r="G85">
         <v>255.3</v>
@@ -8257,37 +8257,37 @@
         <v>214.4</v>
       </c>
       <c r="M85">
-        <v>604.3256891999999</v>
+        <v>611.6067216</v>
       </c>
       <c r="N85">
-        <v>-389.9256892</v>
+        <v>-397.2067216</v>
       </c>
       <c r="O85">
-        <v>-136.47399122</v>
+        <v>-139.02235256</v>
       </c>
       <c r="P85">
-        <v>-253.45169798</v>
+        <v>-258.18436904</v>
       </c>
       <c r="Q85">
-        <v>-185.15169798</v>
+        <v>-189.8843690400001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>1.102680382132555</v>
+        <v>1.168735406015839</v>
       </c>
       <c r="T85">
-        <v>5.192846672623777</v>
+        <v>5.517399589662762</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1241714547983839</v>
+        <v>0.1226932231936412</v>
       </c>
       <c r="W85">
-        <v>0.2065203709585411</v>
+        <v>0.2068689379709394</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3547755851382397</v>
+        <v>0.3505520662675463</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3607675728581232</v>
+        <v>0.3626675728581233</v>
       </c>
       <c r="C86">
-        <v>-539.1337679027642</v>
+        <v>-580.8008322748253</v>
       </c>
       <c r="D86">
-        <v>1799.318232097235</v>
+        <v>1788.529167725174</v>
       </c>
       <c r="E86">
-        <v>1928.652</v>
+        <v>1959.53</v>
       </c>
       <c r="F86">
-        <v>2593.751999999999</v>
+        <v>2624.63</v>
       </c>
       <c r="G86">
         <v>255.3</v>
@@ -8339,37 +8339,37 @@
         <v>214.4</v>
       </c>
       <c r="M86">
-        <v>611.6067215999999</v>
+        <v>618.887754</v>
       </c>
       <c r="N86">
-        <v>-397.2067215999999</v>
+        <v>-404.487754</v>
       </c>
       <c r="O86">
-        <v>-139.02235256</v>
+        <v>-141.5707139</v>
       </c>
       <c r="P86">
-        <v>-258.18436904</v>
+        <v>-262.9170401</v>
       </c>
       <c r="Q86">
-        <v>-189.88436904</v>
+        <v>-194.6170401</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>1.168735406015838</v>
+        <v>1.243597766416894</v>
       </c>
       <c r="T86">
-        <v>5.517399589662759</v>
+        <v>5.88522622897361</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1226932231936413</v>
+        <v>0.1212497735090102</v>
       </c>
       <c r="W86">
-        <v>0.2068689379709394</v>
+        <v>0.2072093034065754</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3505520662675464</v>
+        <v>0.3464279243114576</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3626675728581233</v>
+        <v>0.3645675728581232</v>
       </c>
       <c r="C87">
-        <v>-580.8008322748253</v>
+        <v>-622.3392811661877</v>
       </c>
       <c r="D87">
-        <v>1788.529167725174</v>
+        <v>1777.868718833812</v>
       </c>
       <c r="E87">
-        <v>1959.53</v>
+        <v>1990.408</v>
       </c>
       <c r="F87">
-        <v>2624.63</v>
+        <v>2655.508</v>
       </c>
       <c r="G87">
         <v>255.3</v>
@@ -8421,37 +8421,37 @@
         <v>214.4</v>
       </c>
       <c r="M87">
-        <v>618.887754</v>
+        <v>626.1687863999999</v>
       </c>
       <c r="N87">
-        <v>-404.487754</v>
+        <v>-411.7687864</v>
       </c>
       <c r="O87">
-        <v>-141.5707139</v>
+        <v>-144.11907524</v>
       </c>
       <c r="P87">
-        <v>-262.9170401</v>
+        <v>-267.64971116</v>
       </c>
       <c r="Q87">
-        <v>-194.6170401</v>
+        <v>-199.34971116</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>1.243597766416894</v>
+        <v>1.329154749732387</v>
       </c>
       <c r="T87">
-        <v>5.88522622897361</v>
+        <v>6.305599531043153</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1212497735090102</v>
+        <v>0.1198398924216961</v>
       </c>
       <c r="W87">
-        <v>0.2072093034065754</v>
+        <v>0.2075417533669641</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3464279243114576</v>
+        <v>0.3423996926334174</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3645675728581232</v>
+        <v>0.3664675728581233</v>
       </c>
       <c r="C88">
-        <v>-622.3392811661877</v>
+        <v>-663.7514007707257</v>
       </c>
       <c r="D88">
-        <v>1777.868718833812</v>
+        <v>1767.334599229274</v>
       </c>
       <c r="E88">
-        <v>1990.408</v>
+        <v>2021.286</v>
       </c>
       <c r="F88">
-        <v>2655.508</v>
+        <v>2686.386</v>
       </c>
       <c r="G88">
         <v>255.3</v>
@@ -8503,37 +8503,37 @@
         <v>214.4</v>
       </c>
       <c r="M88">
-        <v>626.1687863999999</v>
+        <v>633.4498188</v>
       </c>
       <c r="N88">
-        <v>-411.7687864</v>
+        <v>-419.0498188</v>
       </c>
       <c r="O88">
-        <v>-144.11907524</v>
+        <v>-146.66743658</v>
       </c>
       <c r="P88">
-        <v>-267.64971116</v>
+        <v>-272.3823822200001</v>
       </c>
       <c r="Q88">
-        <v>-199.34971116</v>
+        <v>-204.0823822200001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>1.329154749732387</v>
+        <v>1.427874345865647</v>
       </c>
       <c r="T88">
-        <v>6.305599531043153</v>
+        <v>6.790645648815704</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1198398924216961</v>
+        <v>0.1184624223938605</v>
       </c>
       <c r="W88">
-        <v>0.2075417533669641</v>
+        <v>0.2078665607995277</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3423996926334174</v>
+        <v>0.3384640639824585</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3664675728581233</v>
+        <v>0.3683675728581233</v>
       </c>
       <c r="C89">
-        <v>-663.7514007707257</v>
+        <v>-705.0394234173991</v>
       </c>
       <c r="D89">
-        <v>1767.334599229274</v>
+        <v>1756.924576582601</v>
       </c>
       <c r="E89">
-        <v>2021.286</v>
+        <v>2052.164</v>
       </c>
       <c r="F89">
-        <v>2686.386</v>
+        <v>2717.264</v>
       </c>
       <c r="G89">
         <v>255.3</v>
@@ -8585,37 +8585,37 @@
         <v>214.4</v>
       </c>
       <c r="M89">
-        <v>633.4498188</v>
+        <v>640.7308512</v>
       </c>
       <c r="N89">
-        <v>-419.0498188</v>
+        <v>-426.3308512</v>
       </c>
       <c r="O89">
-        <v>-146.66743658</v>
+        <v>-149.21579792</v>
       </c>
       <c r="P89">
-        <v>-272.3823822200001</v>
+        <v>-277.11505328</v>
       </c>
       <c r="Q89">
-        <v>-204.0823822200001</v>
+        <v>-208.81505328</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.427874345865647</v>
+        <v>1.543047208021118</v>
       </c>
       <c r="T89">
-        <v>6.790645648815704</v>
+        <v>7.356532786217014</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1184624223938605</v>
+        <v>0.1171162585030212</v>
       </c>
       <c r="W89">
-        <v>0.2078665607995277</v>
+        <v>0.2081839862449876</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3384640639824585</v>
+        <v>0.3346178814372034</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3683675728581233</v>
+        <v>0.3702675728581233</v>
       </c>
       <c r="C90">
-        <v>-705.0394234173991</v>
+        <v>-746.2055291473564</v>
       </c>
       <c r="D90">
-        <v>1756.924576582601</v>
+        <v>1746.636470852643</v>
       </c>
       <c r="E90">
-        <v>2052.164</v>
+        <v>2083.042</v>
       </c>
       <c r="F90">
-        <v>2717.264</v>
+        <v>2748.142</v>
       </c>
       <c r="G90">
         <v>255.3</v>
@@ -8667,37 +8667,37 @@
         <v>214.4</v>
       </c>
       <c r="M90">
-        <v>640.7308512</v>
+        <v>648.0118836</v>
       </c>
       <c r="N90">
-        <v>-426.3308512</v>
+        <v>-433.6118836000001</v>
       </c>
       <c r="O90">
-        <v>-149.21579792</v>
+        <v>-151.76415926</v>
       </c>
       <c r="P90">
-        <v>-277.11505328</v>
+        <v>-281.84772434</v>
       </c>
       <c r="Q90">
-        <v>-208.81505328</v>
+        <v>-213.54772434</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.543047208021118</v>
+        <v>1.679160590568493</v>
       </c>
       <c r="T90">
-        <v>7.356532786217014</v>
+        <v>8.025308494054924</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1171162585030212</v>
+        <v>0.1158003454861333</v>
       </c>
       <c r="W90">
-        <v>0.2081839862449876</v>
+        <v>0.2084942785343698</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3346178814372034</v>
+        <v>0.3308581299603808</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3702675728581233</v>
+        <v>0.3721675728581232</v>
       </c>
       <c r="C91">
-        <v>-746.2055291473564</v>
+        <v>-787.2518472359391</v>
       </c>
       <c r="D91">
-        <v>1746.636470852643</v>
+        <v>1736.468152764061</v>
       </c>
       <c r="E91">
-        <v>2083.042</v>
+        <v>2113.92</v>
       </c>
       <c r="F91">
-        <v>2748.142</v>
+        <v>2779.02</v>
       </c>
       <c r="G91">
         <v>255.3</v>
@@ -8749,37 +8749,37 @@
         <v>214.4</v>
       </c>
       <c r="M91">
-        <v>648.0118836</v>
+        <v>655.292916</v>
       </c>
       <c r="N91">
-        <v>-433.6118836000001</v>
+        <v>-440.892916</v>
       </c>
       <c r="O91">
-        <v>-151.76415926</v>
+        <v>-154.3125206</v>
       </c>
       <c r="P91">
-        <v>-281.84772434</v>
+        <v>-286.5803954</v>
       </c>
       <c r="Q91">
-        <v>-213.54772434</v>
+        <v>-218.2803954000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.679160590568493</v>
+        <v>1.842496649625342</v>
       </c>
       <c r="T91">
-        <v>8.025308494054924</v>
+        <v>8.827839343460417</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1158003454861333</v>
+        <v>0.1145136749807318</v>
       </c>
       <c r="W91">
-        <v>0.2084942785343698</v>
+        <v>0.2087976754395434</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3308581299603808</v>
+        <v>0.3271819285163766</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3721675728581232</v>
+        <v>0.3740675728581233</v>
       </c>
       <c r="C92">
-        <v>-787.2518472359391</v>
+        <v>-828.1804576618358</v>
       </c>
       <c r="D92">
-        <v>1736.468152764061</v>
+        <v>1726.417542338164</v>
       </c>
       <c r="E92">
-        <v>2113.92</v>
+        <v>2144.798</v>
       </c>
       <c r="F92">
-        <v>2779.02</v>
+        <v>2809.898</v>
       </c>
       <c r="G92">
         <v>255.3</v>
@@ -8831,37 +8831,37 @@
         <v>214.4</v>
       </c>
       <c r="M92">
-        <v>655.292916</v>
+        <v>662.5739483999999</v>
       </c>
       <c r="N92">
-        <v>-440.892916</v>
+        <v>-448.1739484</v>
       </c>
       <c r="O92">
-        <v>-154.3125206</v>
+        <v>-156.86088194</v>
       </c>
       <c r="P92">
-        <v>-286.5803954</v>
+        <v>-291.31306646</v>
       </c>
       <c r="Q92">
-        <v>-218.2803954000001</v>
+        <v>-223.01306646</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.842496649625342</v>
+        <v>2.042129610694825</v>
       </c>
       <c r="T92">
-        <v>8.827839343460417</v>
+        <v>9.808710381622689</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1145136749807318</v>
+        <v>0.1132552829479765</v>
       </c>
       <c r="W92">
-        <v>0.2087976754395434</v>
+        <v>0.2090944042808671</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3271819285163766</v>
+        <v>0.3235865227085044</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3740675728581233</v>
+        <v>0.3759675728581233</v>
       </c>
       <c r="C93">
-        <v>-828.1804576618358</v>
+        <v>-868.9933925255089</v>
       </c>
       <c r="D93">
-        <v>1726.417542338164</v>
+        <v>1716.482607474491</v>
       </c>
       <c r="E93">
-        <v>2144.798</v>
+        <v>2175.676</v>
       </c>
       <c r="F93">
-        <v>2809.898</v>
+        <v>2840.776</v>
       </c>
       <c r="G93">
         <v>255.3</v>
@@ -8913,37 +8913,37 @@
         <v>214.4</v>
       </c>
       <c r="M93">
-        <v>662.5739483999999</v>
+        <v>669.8549808</v>
       </c>
       <c r="N93">
-        <v>-448.1739484</v>
+        <v>-455.4549808</v>
       </c>
       <c r="O93">
-        <v>-156.86088194</v>
+        <v>-159.40924328</v>
       </c>
       <c r="P93">
-        <v>-291.31306646</v>
+        <v>-296.04573752</v>
       </c>
       <c r="Q93">
-        <v>-223.01306646</v>
+        <v>-227.7457375200001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>2.042129610694825</v>
+        <v>2.291670812031678</v>
       </c>
       <c r="T93">
-        <v>9.808710381622689</v>
+        <v>11.03479917932552</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1132552829479765</v>
+        <v>0.1120242472637594</v>
       </c>
       <c r="W93">
-        <v>0.2090944042808671</v>
+        <v>0.2093846824952056</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3235865227085044</v>
+        <v>0.3200692778964553</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3759675728581233</v>
+        <v>0.3778675728581232</v>
       </c>
       <c r="C94">
-        <v>-868.9933925255089</v>
+        <v>-909.6926374189241</v>
       </c>
       <c r="D94">
-        <v>1716.482607474491</v>
+        <v>1706.661362581076</v>
       </c>
       <c r="E94">
-        <v>2175.676</v>
+        <v>2206.554</v>
       </c>
       <c r="F94">
-        <v>2840.776</v>
+        <v>2871.654</v>
       </c>
       <c r="G94">
         <v>255.3</v>
@@ -8995,37 +8995,37 @@
         <v>214.4</v>
       </c>
       <c r="M94">
-        <v>669.8549808</v>
+        <v>677.1360132</v>
       </c>
       <c r="N94">
-        <v>-455.4549808</v>
+        <v>-462.7360132</v>
       </c>
       <c r="O94">
-        <v>-159.40924328</v>
+        <v>-161.95760462</v>
       </c>
       <c r="P94">
-        <v>-296.04573752</v>
+        <v>-300.77840858</v>
       </c>
       <c r="Q94">
-        <v>-227.7457375200001</v>
+        <v>-232.47840858</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>2.291670812031678</v>
+        <v>2.612509499464776</v>
       </c>
       <c r="T94">
-        <v>11.03479917932552</v>
+        <v>12.61119906208632</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1120242472637594</v>
+        <v>0.1108196854652243</v>
       </c>
       <c r="W94">
-        <v>0.2093846824952056</v>
+        <v>0.2096687181673001</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3200692778964553</v>
+        <v>0.3166276727577838</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3778675728581232</v>
+        <v>0.3797675728581232</v>
       </c>
       <c r="C95">
-        <v>-909.6926374189241</v>
+        <v>-950.2801327485242</v>
       </c>
       <c r="D95">
-        <v>1706.661362581076</v>
+        <v>1696.951867251476</v>
       </c>
       <c r="E95">
-        <v>2206.554</v>
+        <v>2237.432</v>
       </c>
       <c r="F95">
-        <v>2871.654</v>
+        <v>2902.532</v>
       </c>
       <c r="G95">
         <v>255.3</v>
@@ -9077,37 +9077,37 @@
         <v>214.4</v>
       </c>
       <c r="M95">
-        <v>677.1360132</v>
+        <v>684.4170455999999</v>
       </c>
       <c r="N95">
-        <v>-462.7360132</v>
+        <v>-470.0170456</v>
       </c>
       <c r="O95">
-        <v>-161.95760462</v>
+        <v>-164.50596596</v>
       </c>
       <c r="P95">
-        <v>-300.77840858</v>
+        <v>-305.51107964</v>
       </c>
       <c r="Q95">
-        <v>-232.47840858</v>
+        <v>-237.21107964</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>2.612509499464776</v>
+        <v>3.040294416042239</v>
       </c>
       <c r="T95">
-        <v>12.61119906208632</v>
+        <v>14.71306557243404</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1108196854652243</v>
+        <v>0.1096407526411262</v>
       </c>
       <c r="W95">
-        <v>0.2096687181673001</v>
+        <v>0.2099467105272224</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3166276727577838</v>
+        <v>0.3132592932603606</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3797675728581232</v>
+        <v>0.3816675728581233</v>
       </c>
       <c r="C96">
-        <v>-950.2801327485242</v>
+        <v>-990.7577750133048</v>
       </c>
       <c r="D96">
-        <v>1696.951867251476</v>
+        <v>1687.352224986695</v>
       </c>
       <c r="E96">
-        <v>2237.432</v>
+        <v>2268.31</v>
       </c>
       <c r="F96">
-        <v>2902.532</v>
+        <v>2933.41</v>
       </c>
       <c r="G96">
         <v>255.3</v>
@@ -9159,37 +9159,37 @@
         <v>214.4</v>
       </c>
       <c r="M96">
-        <v>684.4170455999999</v>
+        <v>691.698078</v>
       </c>
       <c r="N96">
-        <v>-470.0170456</v>
+        <v>-477.298078</v>
       </c>
       <c r="O96">
-        <v>-164.50596596</v>
+        <v>-167.0543273</v>
       </c>
       <c r="P96">
-        <v>-305.51107964</v>
+        <v>-310.2437507</v>
       </c>
       <c r="Q96">
-        <v>-237.21107964</v>
+        <v>-241.9437507</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>3.040294416042239</v>
+        <v>3.639193299250688</v>
       </c>
       <c r="T96">
-        <v>14.71306557243404</v>
+        <v>17.65567868692086</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1096407526411262</v>
+        <v>0.1084866394554301</v>
       </c>
       <c r="W96">
-        <v>0.2099467105272224</v>
+        <v>0.2102188504164096</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3132592932603606</v>
+        <v>0.3099618270155147</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3816675728581233</v>
+        <v>0.3835675728581233</v>
       </c>
       <c r="C97">
-        <v>-990.7577750133048</v>
+        <v>-1031.127418039739</v>
       </c>
       <c r="D97">
-        <v>1687.352224986695</v>
+        <v>1677.860581960261</v>
       </c>
       <c r="E97">
-        <v>2268.31</v>
+        <v>2299.188</v>
       </c>
       <c r="F97">
-        <v>2933.41</v>
+        <v>2964.288</v>
       </c>
       <c r="G97">
         <v>255.3</v>
@@ -9241,37 +9241,37 @@
         <v>214.4</v>
       </c>
       <c r="M97">
-        <v>691.698078</v>
+        <v>698.9791104000001</v>
       </c>
       <c r="N97">
-        <v>-477.298078</v>
+        <v>-484.5791104000001</v>
       </c>
       <c r="O97">
-        <v>-167.0543273</v>
+        <v>-169.60268864</v>
       </c>
       <c r="P97">
-        <v>-310.2437507</v>
+        <v>-314.9764217600001</v>
       </c>
       <c r="Q97">
-        <v>-241.9437507</v>
+        <v>-246.6764217600001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>3.639193299250688</v>
+        <v>4.537541624063363</v>
       </c>
       <c r="T97">
-        <v>17.65567868692086</v>
+        <v>22.06959835865108</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1084866394554301</v>
+        <v>0.1073565702944361</v>
       </c>
       <c r="W97">
-        <v>0.2102188504164096</v>
+        <v>0.210485320724572</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3099618270155147</v>
+        <v>0.306733057984103</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3835675728581233</v>
+        <v>0.3854675728581233</v>
       </c>
       <c r="C98">
-        <v>-1031.127418039739</v>
+        <v>-1071.390874175277</v>
       </c>
       <c r="D98">
-        <v>1677.860581960261</v>
+        <v>1668.475125824723</v>
       </c>
       <c r="E98">
-        <v>2299.188</v>
+        <v>2330.066</v>
       </c>
       <c r="F98">
-        <v>2964.288</v>
+        <v>2995.166</v>
       </c>
       <c r="G98">
         <v>255.3</v>
@@ -9323,37 +9323,37 @@
         <v>214.4</v>
       </c>
       <c r="M98">
-        <v>698.9791104</v>
+        <v>706.2601427999999</v>
       </c>
       <c r="N98">
-        <v>-484.5791104</v>
+        <v>-491.8601427999999</v>
       </c>
       <c r="O98">
-        <v>-169.60268864</v>
+        <v>-172.15104998</v>
       </c>
       <c r="P98">
-        <v>-314.97642176</v>
+        <v>-319.70909282</v>
       </c>
       <c r="Q98">
-        <v>-246.67642176</v>
+        <v>-251.40909282</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>4.53754162406335</v>
+        <v>6.034788832084468</v>
       </c>
       <c r="T98">
-        <v>22.06959835865102</v>
+        <v>29.42613114486803</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1073565702944361</v>
+        <v>0.1062498015285141</v>
       </c>
       <c r="W98">
-        <v>0.210485320724572</v>
+        <v>0.2107462967995764</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3067330579841031</v>
+        <v>0.3035708615100402</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3854675728581233</v>
+        <v>0.3873675728581233</v>
       </c>
       <c r="C99">
-        <v>-1071.390874175277</v>
+        <v>-1111.549915441989</v>
       </c>
       <c r="D99">
-        <v>1668.475125824723</v>
+        <v>1659.19408455801</v>
       </c>
       <c r="E99">
-        <v>2330.066</v>
+        <v>2360.944</v>
       </c>
       <c r="F99">
-        <v>2995.166</v>
+        <v>3026.044</v>
       </c>
       <c r="G99">
         <v>255.3</v>
@@ -9405,37 +9405,37 @@
         <v>214.4</v>
       </c>
       <c r="M99">
-        <v>706.2601427999999</v>
+        <v>713.5411752</v>
       </c>
       <c r="N99">
-        <v>-491.8601427999999</v>
+        <v>-499.1411752</v>
       </c>
       <c r="O99">
-        <v>-172.15104998</v>
+        <v>-174.69941132</v>
       </c>
       <c r="P99">
-        <v>-319.70909282</v>
+        <v>-324.4417638800001</v>
       </c>
       <c r="Q99">
-        <v>-251.40909282</v>
+        <v>-256.1417638800001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>6.034788832084468</v>
+        <v>9.029283248126701</v>
       </c>
       <c r="T99">
-        <v>29.42613114486803</v>
+        <v>44.13919671730204</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1062498015285141</v>
+        <v>0.1051656198802639</v>
       </c>
       <c r="W99">
-        <v>0.2107462967995764</v>
+        <v>0.2110019468322338</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3035708615100402</v>
+        <v>0.3004731996578969</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3873675728581233</v>
+        <v>0.3892675728581233</v>
       </c>
       <c r="C100">
-        <v>-1111.549915441989</v>
+        <v>-1151.606274651936</v>
       </c>
       <c r="D100">
-        <v>1659.19408455801</v>
+        <v>1650.015725348064</v>
       </c>
       <c r="E100">
-        <v>2360.944</v>
+        <v>2391.822</v>
       </c>
       <c r="F100">
-        <v>3026.044</v>
+        <v>3056.922</v>
       </c>
       <c r="G100">
         <v>255.3</v>
@@ -9487,37 +9487,37 @@
         <v>214.4</v>
       </c>
       <c r="M100">
-        <v>713.5411752</v>
+        <v>720.8222076</v>
       </c>
       <c r="N100">
-        <v>-499.1411752</v>
+        <v>-506.4222076</v>
       </c>
       <c r="O100">
-        <v>-174.69941132</v>
+        <v>-177.24777266</v>
       </c>
       <c r="P100">
-        <v>-324.4417638800001</v>
+        <v>-329.17443494</v>
       </c>
       <c r="Q100">
-        <v>-256.1417638800001</v>
+        <v>-260.87443494</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>9.029283248126701</v>
+        <v>18.01276649625341</v>
       </c>
       <c r="T100">
-        <v>44.13919671730204</v>
+        <v>88.2783934346041</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1051656198802639</v>
+        <v>0.1041033408915744</v>
       </c>
       <c r="W100">
-        <v>0.2110019468322338</v>
+        <v>0.2112524322177668</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3004731996578969</v>
+        <v>0.2974381168330696</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3892675728581233</v>
-      </c>
-      <c r="C101">
-        <v>-1151.606274651936</v>
-      </c>
-      <c r="D101">
-        <v>1650.015725348064</v>
-      </c>
-      <c r="E101">
-        <v>2391.822</v>
-      </c>
-      <c r="F101">
-        <v>3056.922</v>
-      </c>
-      <c r="G101">
-        <v>255.3</v>
-      </c>
-      <c r="H101">
-        <v>2422.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>282.7</v>
-      </c>
-      <c r="K101">
-        <v>68.29999999999998</v>
-      </c>
-      <c r="L101">
-        <v>214.4</v>
-      </c>
-      <c r="M101">
-        <v>720.8222076</v>
-      </c>
-      <c r="N101">
-        <v>-506.4222076</v>
-      </c>
-      <c r="O101">
-        <v>-177.24777266</v>
-      </c>
-      <c r="P101">
-        <v>-329.17443494</v>
-      </c>
-      <c r="Q101">
-        <v>-260.87443494</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>18.01276649625341</v>
-      </c>
-      <c r="T101">
-        <v>88.2783934346041</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1041033408915744</v>
-      </c>
-      <c r="W101">
-        <v>0.2112524322177668</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2974381168330696</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
